--- a/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
+++ b/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
@@ -1175,7 +1175,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1224,7 +1224,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1268,7 +1268,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1317,7 +1317,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1361,7 +1361,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1410,7 +1410,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1471,7 +1471,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1537,7 +1537,7 @@
         <xdr:cNvPr id="6145" name="AutoShape 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7540,15 +7540,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" xsi:nil="true"/>
@@ -7557,6 +7548,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7579,14 +7579,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B672EAD0-EA6C-460E-95E6-5BDD1102E907}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7595,4 +7587,12 @@
     <ds:schemaRef ds:uri="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
+++ b/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
@@ -9,16 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21195" windowHeight="8085" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21195" windowHeight="8085" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="PTR base data" sheetId="5" r:id="rId2"/>
     <sheet name="Example" sheetId="6" r:id="rId3"/>
     <sheet name="Truss design" sheetId="4" r:id="rId4"/>
-    <sheet name="Instrumentation" sheetId="7" r:id="rId5"/>
+    <sheet name="Truss design 2.0" sheetId="8" r:id="rId5"/>
+    <sheet name="Instrumentation" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="237">
   <si>
     <t>(Materials selection in mechanical design, pp 12)</t>
   </si>
@@ -794,11 +795,71 @@
   <si>
     <t>Módulo de Conversión de Analógico a Digital Placa de Adquisición de Señal ADC de Alta Precisión de 8 Canales Y 24 Bits Convierta Señales Analógicas en Señales Digitales : Amazon.com.mx: Industria, Empresas y Ciencia</t>
   </si>
+  <si>
+    <t>Truss by points</t>
+  </si>
+  <si>
+    <t>Back support</t>
+  </si>
+  <si>
+    <t>SRM base</t>
+  </si>
+  <si>
+    <t>x-z</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>Length of member</t>
+  </si>
+  <si>
+    <t>Trans area</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>Caliber (thick.)</t>
+  </si>
+  <si>
+    <t>mm2</t>
+  </si>
+  <si>
+    <t>Input cell</t>
+  </si>
+  <si>
+    <t>Analysis by member of truss (tension or compression)</t>
+  </si>
+  <si>
+    <t>Back support group</t>
+  </si>
+  <si>
+    <t>Short members</t>
+  </si>
+  <si>
+    <t>Large member</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -845,7 +906,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -867,6 +928,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1067,7 +1134,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1130,6 +1197,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1153,6 +1227,4343 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.2337806693626498E-2"/>
+          <c:y val="5.8666666666666666E-2"/>
+          <c:w val="0.76945599159388001"/>
+          <c:h val="0.82561721784776898"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$15:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$15:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$17:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$17:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$19:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$19:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$21:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$21:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$23:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$23:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$15:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$15:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$17:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$17:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$19:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$19:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$21:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$21:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$23:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$23:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="-1316492864"/>
+        <c:axId val="-1316504832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="-1316492864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1316504832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="-1316504832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1316492864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15940839358628936"/>
+          <c:y val="7.1812639435779868E-2"/>
+          <c:w val="0.76387538787595011"/>
+          <c:h val="0.78654168423000603"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$31:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$31:$D$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$33:$C$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$33:$D$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$35:$C$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$35:$D$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$37:$C$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$37:$D$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="-1390972832"/>
+        <c:axId val="-1390973920"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="-1390972832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1390973920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="-1390973920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1390972832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.2337806693626498E-2"/>
+          <c:y val="5.8666666666666666E-2"/>
+          <c:w val="0.62088127533483006"/>
+          <c:h val="0.82561721784776898"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$15:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$15:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$17:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$17:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$19:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$19:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$21:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$21:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$23:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$23:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$15:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$15:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$17:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$17:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$19:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$19:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$21:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$21:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$C$23:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$23:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$E$31:$E$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$31:$D$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$E$33:$E$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$33:$D$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$E$35:$E$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$35:$D$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Truss design 2.0'!$B$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$E$37:$E$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Truss design 2.0'!$D$37:$D$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="-1316492320"/>
+        <c:axId val="-1316501024"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="-1316492320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1316501024"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="-1316501024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="150"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1316492320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1518,6 +5929,103 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>14286</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>100853</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19048</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>302559</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>174811</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>671513</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2141,12 +6649,12 @@
     <col min="11" max="11" width="18" style="4" customWidth="1"/>
     <col min="12" max="12" width="23.25" style="4" customWidth="1"/>
     <col min="13" max="13" width="8.875" style="4"/>
-    <col min="14" max="14" width="20.25" style="4" customWidth="1"/>
+    <col min="14" max="14" width="30.875" style="4" customWidth="1"/>
     <col min="15" max="16384" width="8.875" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15" thickBot="1"/>
-    <row r="3" spans="2:14" ht="40.9" customHeight="1" thickBot="1">
+    <row r="3" spans="2:14" ht="40.5" customHeight="1" thickBot="1">
       <c r="B3" s="2" t="s">
         <v>38</v>
       </c>
@@ -2168,12 +6676,12 @@
       <c r="H3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="24"/>
-    </row>
-    <row r="4" spans="2:14" ht="18.600000000000001" customHeight="1">
+      <c r="L3" s="29"/>
+    </row>
+    <row r="4" spans="2:14" ht="29.25" customHeight="1">
       <c r="B4" s="6" t="s">
         <v>46</v>
       </c>
@@ -5279,6 +9787,444 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:F38"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="16.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="15" thickBot="1"/>
+    <row r="2" spans="2:6" ht="15" thickBot="1">
+      <c r="B2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="28"/>
+      <c r="F2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="25">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" s="26">
+        <f>C6/25.4</f>
+        <v>0.78740157480314965</v>
+      </c>
+      <c r="F6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7">
+        <f>E7*25.4</f>
+        <v>25.4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E7" s="25">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8">
+        <f>E8*25.4</f>
+        <v>25.4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" s="25">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="26">
+        <f>E9*25.4</f>
+        <v>2.3812499999999996</v>
+      </c>
+      <c r="D9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="27">
+        <f>(3/32)</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="26">
+        <f>(C7*C8)-((C7-2*C9)*(C8-2*C9))</f>
+        <v>219.25359374999999</v>
+      </c>
+      <c r="D10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="28.5">
+      <c r="B14" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f>C6</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <f>C16</f>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f>D16</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="C18">
+        <f>C6</f>
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <f>C6</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <f>C6</f>
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <f>C6</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="C20">
+        <f>C19</f>
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <f>C20</f>
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <f>C19</f>
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <f>D19</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="C24">
+        <f>C15</f>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f>D15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="F25" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E26">
+        <f>C26/25.4</f>
+        <v>0.78740157480314965</v>
+      </c>
+      <c r="F26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C27">
+        <f>40</f>
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>228</v>
+      </c>
+      <c r="E27">
+        <f>C27/25.4</f>
+        <v>1.5748031496062993</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30" t="s">
+        <v>223</v>
+      </c>
+      <c r="E30" t="s">
+        <v>222</v>
+      </c>
+      <c r="F30" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <f>D23</f>
+        <v>20</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="C32">
+        <f>C26</f>
+        <v>20</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <f>C26+E31</f>
+        <v>40</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33">
+        <v>2.1</v>
+      </c>
+      <c r="C33">
+        <f>C32</f>
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f>E32</f>
+        <v>40</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="C34">
+        <f>C33+C26</f>
+        <v>40</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <f>E33+C26</f>
+        <v>60</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35">
+        <v>3.1</v>
+      </c>
+      <c r="C35">
+        <f>C34</f>
+        <v>40</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <f>E34</f>
+        <v>60</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="C36">
+        <f>C35+C27</f>
+        <v>80</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <f>E35+C27</f>
+        <v>100</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C37">
+        <f>C36</f>
+        <v>80</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <f>E36</f>
+        <v>100</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="C38">
+        <f>C37+C27</f>
+        <v>120</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <f>E37+C27</f>
+        <v>140</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:J231"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -5298,2013 +10244,2013 @@
       </c>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="25" t="e" vm="1">
+      <c r="B6" s="30" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
       <c r="J6" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
       <c r="J7" s="19" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
       <c r="J8" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
       <c r="J9" s="19" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
       <c r="J13" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
       <c r="J17" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
     </row>
     <row r="26" spans="2:10">
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
     </row>
     <row r="32" spans="2:10">
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
     </row>
     <row r="38" spans="2:8">
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
     </row>
     <row r="43" spans="2:8">
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
     </row>
     <row r="45" spans="2:8">
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
     </row>
     <row r="49" spans="2:8">
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="25"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
     </row>
     <row r="50" spans="2:8">
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
     </row>
     <row r="51" spans="2:8">
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
     </row>
     <row r="52" spans="2:8">
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
     </row>
     <row r="53" spans="2:8">
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
     </row>
     <row r="54" spans="2:8">
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
     </row>
     <row r="55" spans="2:8">
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
     </row>
     <row r="56" spans="2:8">
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
     </row>
     <row r="57" spans="2:8">
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
     </row>
     <row r="58" spans="2:8">
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
     </row>
     <row r="59" spans="2:8">
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="25"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
     </row>
     <row r="60" spans="2:8">
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
     </row>
     <row r="61" spans="2:8">
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
     </row>
     <row r="62" spans="2:8">
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
     </row>
     <row r="63" spans="2:8">
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
     </row>
     <row r="64" spans="2:8">
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
     </row>
     <row r="67" spans="2:8">
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
     </row>
     <row r="69" spans="2:8">
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="25"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
     </row>
     <row r="71" spans="2:8">
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
     </row>
     <row r="72" spans="2:8">
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
     </row>
     <row r="73" spans="2:8">
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
     </row>
     <row r="74" spans="2:8">
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
     </row>
     <row r="75" spans="2:8">
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
     </row>
     <row r="76" spans="2:8">
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
     </row>
     <row r="77" spans="2:8">
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="25"/>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
     </row>
     <row r="78" spans="2:8">
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
     </row>
     <row r="79" spans="2:8">
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
     </row>
     <row r="80" spans="2:8">
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
     </row>
     <row r="81" spans="2:8">
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="25"/>
-      <c r="E81" s="25"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="25"/>
-      <c r="H81" s="25"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
     </row>
     <row r="82" spans="2:8">
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="25"/>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
+      <c r="H82" s="30"/>
     </row>
     <row r="83" spans="2:8">
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
     </row>
     <row r="84" spans="2:8">
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
+      <c r="H84" s="30"/>
     </row>
     <row r="85" spans="2:8">
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="25"/>
-      <c r="E85" s="25"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="25"/>
-      <c r="H85" s="25"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
     </row>
     <row r="86" spans="2:8">
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25"/>
-      <c r="F86" s="25"/>
-      <c r="G86" s="25"/>
-      <c r="H86" s="25"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
     </row>
     <row r="87" spans="2:8">
-      <c r="B87" s="25"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="25"/>
-      <c r="E87" s="25"/>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25"/>
-      <c r="H87" s="25"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
     </row>
     <row r="88" spans="2:8">
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
+      <c r="H88" s="30"/>
     </row>
     <row r="89" spans="2:8">
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25"/>
-      <c r="H89" s="25"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
+      <c r="G89" s="30"/>
+      <c r="H89" s="30"/>
     </row>
     <row r="90" spans="2:8">
-      <c r="B90" s="25"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25"/>
-      <c r="H90" s="25"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
     </row>
     <row r="91" spans="2:8">
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="25"/>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
-      <c r="H91" s="25"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="30"/>
+      <c r="H91" s="30"/>
     </row>
     <row r="92" spans="2:8">
-      <c r="B92" s="25"/>
-      <c r="C92" s="25"/>
-      <c r="D92" s="25"/>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="30"/>
     </row>
     <row r="93" spans="2:8">
-      <c r="B93" s="25"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="25"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="30"/>
+      <c r="H93" s="30"/>
     </row>
     <row r="94" spans="2:8">
-      <c r="B94" s="25"/>
-      <c r="C94" s="25"/>
-      <c r="D94" s="25"/>
-      <c r="E94" s="25"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
-      <c r="H94" s="25"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+      <c r="H94" s="30"/>
     </row>
     <row r="95" spans="2:8">
-      <c r="B95" s="25"/>
-      <c r="C95" s="25"/>
-      <c r="D95" s="25"/>
-      <c r="E95" s="25"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="25"/>
-      <c r="H95" s="25"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
+      <c r="G95" s="30"/>
+      <c r="H95" s="30"/>
     </row>
     <row r="96" spans="2:8">
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="25"/>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="30"/>
     </row>
     <row r="97" spans="2:8">
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="25"/>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+      <c r="H97" s="30"/>
     </row>
     <row r="98" spans="2:8">
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="25"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="30"/>
+      <c r="H98" s="30"/>
     </row>
     <row r="99" spans="2:8">
-      <c r="B99" s="25"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="25"/>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="25"/>
-      <c r="H99" s="25"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
     </row>
     <row r="100" spans="2:8">
-      <c r="B100" s="25"/>
-      <c r="C100" s="25"/>
-      <c r="D100" s="25"/>
-      <c r="E100" s="25"/>
-      <c r="F100" s="25"/>
-      <c r="G100" s="25"/>
-      <c r="H100" s="25"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
     </row>
     <row r="101" spans="2:8">
-      <c r="B101" s="25"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
     </row>
     <row r="102" spans="2:8">
-      <c r="B102" s="25"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="25"/>
-      <c r="E102" s="25"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
-      <c r="H102" s="25"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30"/>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
+      <c r="H102" s="30"/>
     </row>
     <row r="103" spans="2:8">
-      <c r="B103" s="25"/>
-      <c r="C103" s="25"/>
-      <c r="D103" s="25"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
-      <c r="H103" s="25"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+      <c r="H103" s="30"/>
     </row>
     <row r="104" spans="2:8">
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="25"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="25"/>
-      <c r="H104" s="25"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
+      <c r="H104" s="30"/>
     </row>
     <row r="105" spans="2:8">
-      <c r="B105" s="25"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="25"/>
-      <c r="E105" s="25"/>
-      <c r="F105" s="25"/>
-      <c r="G105" s="25"/>
-      <c r="H105" s="25"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
+      <c r="D105" s="30"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
     </row>
     <row r="106" spans="2:8">
-      <c r="B106" s="25"/>
-      <c r="C106" s="25"/>
-      <c r="D106" s="25"/>
-      <c r="E106" s="25"/>
-      <c r="F106" s="25"/>
-      <c r="G106" s="25"/>
-      <c r="H106" s="25"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="30"/>
+      <c r="D106" s="30"/>
+      <c r="E106" s="30"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+      <c r="H106" s="30"/>
     </row>
     <row r="107" spans="2:8">
-      <c r="B107" s="25"/>
-      <c r="C107" s="25"/>
-      <c r="D107" s="25"/>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
-      <c r="H107" s="25"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+      <c r="D107" s="30"/>
+      <c r="E107" s="30"/>
+      <c r="F107" s="30"/>
+      <c r="G107" s="30"/>
+      <c r="H107" s="30"/>
     </row>
     <row r="108" spans="2:8">
-      <c r="B108" s="25"/>
-      <c r="C108" s="25"/>
-      <c r="D108" s="25"/>
-      <c r="E108" s="25"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="25"/>
-      <c r="H108" s="25"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30"/>
+      <c r="D108" s="30"/>
+      <c r="E108" s="30"/>
+      <c r="F108" s="30"/>
+      <c r="G108" s="30"/>
+      <c r="H108" s="30"/>
     </row>
     <row r="109" spans="2:8">
-      <c r="B109" s="25"/>
-      <c r="C109" s="25"/>
-      <c r="D109" s="25"/>
-      <c r="E109" s="25"/>
-      <c r="F109" s="25"/>
-      <c r="G109" s="25"/>
-      <c r="H109" s="25"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="30"/>
+      <c r="D109" s="30"/>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="30"/>
+      <c r="H109" s="30"/>
     </row>
     <row r="110" spans="2:8">
-      <c r="B110" s="25"/>
-      <c r="C110" s="25"/>
-      <c r="D110" s="25"/>
-      <c r="E110" s="25"/>
-      <c r="F110" s="25"/>
-      <c r="G110" s="25"/>
-      <c r="H110" s="25"/>
+      <c r="B110" s="30"/>
+      <c r="C110" s="30"/>
+      <c r="D110" s="30"/>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="30"/>
+      <c r="H110" s="30"/>
     </row>
     <row r="111" spans="2:8">
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="25"/>
-      <c r="E111" s="25"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="25"/>
-      <c r="H111" s="25"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="30"/>
+      <c r="D111" s="30"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="30"/>
+      <c r="H111" s="30"/>
     </row>
     <row r="112" spans="2:8">
-      <c r="B112" s="25"/>
-      <c r="C112" s="25"/>
-      <c r="D112" s="25"/>
-      <c r="E112" s="25"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="25"/>
-      <c r="H112" s="25"/>
+      <c r="B112" s="30"/>
+      <c r="C112" s="30"/>
+      <c r="D112" s="30"/>
+      <c r="E112" s="30"/>
+      <c r="F112" s="30"/>
+      <c r="G112" s="30"/>
+      <c r="H112" s="30"/>
     </row>
     <row r="113" spans="2:8">
-      <c r="B113" s="25"/>
-      <c r="C113" s="25"/>
-      <c r="D113" s="25"/>
-      <c r="E113" s="25"/>
-      <c r="F113" s="25"/>
-      <c r="G113" s="25"/>
-      <c r="H113" s="25"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="30"/>
     </row>
     <row r="114" spans="2:8">
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
-      <c r="D114" s="25"/>
-      <c r="E114" s="25"/>
-      <c r="F114" s="25"/>
-      <c r="G114" s="25"/>
-      <c r="H114" s="25"/>
+      <c r="B114" s="30"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="30"/>
+      <c r="E114" s="30"/>
+      <c r="F114" s="30"/>
+      <c r="G114" s="30"/>
+      <c r="H114" s="30"/>
     </row>
     <row r="115" spans="2:8">
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="25"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="25"/>
-      <c r="G115" s="25"/>
-      <c r="H115" s="25"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="30"/>
+      <c r="D115" s="30"/>
+      <c r="E115" s="30"/>
+      <c r="F115" s="30"/>
+      <c r="G115" s="30"/>
+      <c r="H115" s="30"/>
     </row>
     <row r="116" spans="2:8">
-      <c r="B116" s="25"/>
-      <c r="C116" s="25"/>
-      <c r="D116" s="25"/>
-      <c r="E116" s="25"/>
-      <c r="F116" s="25"/>
-      <c r="G116" s="25"/>
-      <c r="H116" s="25"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="30"/>
+      <c r="D116" s="30"/>
+      <c r="E116" s="30"/>
+      <c r="F116" s="30"/>
+      <c r="G116" s="30"/>
+      <c r="H116" s="30"/>
     </row>
     <row r="117" spans="2:8">
-      <c r="B117" s="25"/>
-      <c r="C117" s="25"/>
-      <c r="D117" s="25"/>
-      <c r="E117" s="25"/>
-      <c r="F117" s="25"/>
-      <c r="G117" s="25"/>
-      <c r="H117" s="25"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="30"/>
+      <c r="D117" s="30"/>
+      <c r="E117" s="30"/>
+      <c r="F117" s="30"/>
+      <c r="G117" s="30"/>
+      <c r="H117" s="30"/>
     </row>
     <row r="118" spans="2:8">
-      <c r="B118" s="25"/>
-      <c r="C118" s="25"/>
-      <c r="D118" s="25"/>
-      <c r="E118" s="25"/>
-      <c r="F118" s="25"/>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30"/>
+      <c r="E118" s="30"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="30"/>
+      <c r="H118" s="30"/>
     </row>
     <row r="119" spans="2:8">
-      <c r="B119" s="25"/>
-      <c r="C119" s="25"/>
-      <c r="D119" s="25"/>
-      <c r="E119" s="25"/>
-      <c r="F119" s="25"/>
-      <c r="G119" s="25"/>
-      <c r="H119" s="25"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="30"/>
+      <c r="E119" s="30"/>
+      <c r="F119" s="30"/>
+      <c r="G119" s="30"/>
+      <c r="H119" s="30"/>
     </row>
     <row r="120" spans="2:8">
-      <c r="B120" s="25"/>
-      <c r="C120" s="25"/>
-      <c r="D120" s="25"/>
-      <c r="E120" s="25"/>
-      <c r="F120" s="25"/>
-      <c r="G120" s="25"/>
-      <c r="H120" s="25"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="30"/>
+      <c r="D120" s="30"/>
+      <c r="E120" s="30"/>
+      <c r="F120" s="30"/>
+      <c r="G120" s="30"/>
+      <c r="H120" s="30"/>
     </row>
     <row r="121" spans="2:8">
-      <c r="B121" s="25"/>
-      <c r="C121" s="25"/>
-      <c r="D121" s="25"/>
-      <c r="E121" s="25"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="25"/>
-      <c r="H121" s="25"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="30"/>
+      <c r="D121" s="30"/>
+      <c r="E121" s="30"/>
+      <c r="F121" s="30"/>
+      <c r="G121" s="30"/>
+      <c r="H121" s="30"/>
     </row>
     <row r="122" spans="2:8">
-      <c r="B122" s="25"/>
-      <c r="C122" s="25"/>
-      <c r="D122" s="25"/>
-      <c r="E122" s="25"/>
-      <c r="F122" s="25"/>
-      <c r="G122" s="25"/>
-      <c r="H122" s="25"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="30"/>
+      <c r="E122" s="30"/>
+      <c r="F122" s="30"/>
+      <c r="G122" s="30"/>
+      <c r="H122" s="30"/>
     </row>
     <row r="123" spans="2:8">
-      <c r="B123" s="25"/>
-      <c r="C123" s="25"/>
-      <c r="D123" s="25"/>
-      <c r="E123" s="25"/>
-      <c r="F123" s="25"/>
-      <c r="G123" s="25"/>
-      <c r="H123" s="25"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="30"/>
+      <c r="H123" s="30"/>
     </row>
     <row r="124" spans="2:8">
-      <c r="B124" s="25"/>
-      <c r="C124" s="25"/>
-      <c r="D124" s="25"/>
-      <c r="E124" s="25"/>
-      <c r="F124" s="25"/>
-      <c r="G124" s="25"/>
-      <c r="H124" s="25"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="30"/>
+      <c r="D124" s="30"/>
+      <c r="E124" s="30"/>
+      <c r="F124" s="30"/>
+      <c r="G124" s="30"/>
+      <c r="H124" s="30"/>
     </row>
     <row r="125" spans="2:8">
-      <c r="B125" s="25"/>
-      <c r="C125" s="25"/>
-      <c r="D125" s="25"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="25"/>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+      <c r="D125" s="30"/>
+      <c r="E125" s="30"/>
+      <c r="F125" s="30"/>
+      <c r="G125" s="30"/>
+      <c r="H125" s="30"/>
     </row>
     <row r="126" spans="2:8">
-      <c r="B126" s="25"/>
-      <c r="C126" s="25"/>
-      <c r="D126" s="25"/>
-      <c r="E126" s="25"/>
-      <c r="F126" s="25"/>
-      <c r="G126" s="25"/>
-      <c r="H126" s="25"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="30"/>
+      <c r="D126" s="30"/>
+      <c r="E126" s="30"/>
+      <c r="F126" s="30"/>
+      <c r="G126" s="30"/>
+      <c r="H126" s="30"/>
     </row>
     <row r="127" spans="2:8">
-      <c r="B127" s="25"/>
-      <c r="C127" s="25"/>
-      <c r="D127" s="25"/>
-      <c r="E127" s="25"/>
-      <c r="F127" s="25"/>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="30"/>
+      <c r="D127" s="30"/>
+      <c r="E127" s="30"/>
+      <c r="F127" s="30"/>
+      <c r="G127" s="30"/>
+      <c r="H127" s="30"/>
     </row>
     <row r="128" spans="2:8">
-      <c r="B128" s="25"/>
-      <c r="C128" s="25"/>
-      <c r="D128" s="25"/>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="30"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="30"/>
+      <c r="G128" s="30"/>
+      <c r="H128" s="30"/>
     </row>
     <row r="129" spans="2:8">
-      <c r="B129" s="25"/>
-      <c r="C129" s="25"/>
-      <c r="D129" s="25"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="25"/>
-      <c r="G129" s="25"/>
-      <c r="H129" s="25"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="30"/>
+      <c r="D129" s="30"/>
+      <c r="E129" s="30"/>
+      <c r="F129" s="30"/>
+      <c r="G129" s="30"/>
+      <c r="H129" s="30"/>
     </row>
     <row r="130" spans="2:8">
-      <c r="B130" s="25"/>
-      <c r="C130" s="25"/>
-      <c r="D130" s="25"/>
-      <c r="E130" s="25"/>
-      <c r="F130" s="25"/>
-      <c r="G130" s="25"/>
-      <c r="H130" s="25"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="30"/>
+      <c r="F130" s="30"/>
+      <c r="G130" s="30"/>
+      <c r="H130" s="30"/>
     </row>
     <row r="131" spans="2:8">
-      <c r="B131" s="25"/>
-      <c r="C131" s="25"/>
-      <c r="D131" s="25"/>
-      <c r="E131" s="25"/>
-      <c r="F131" s="25"/>
-      <c r="G131" s="25"/>
-      <c r="H131" s="25"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+      <c r="D131" s="30"/>
+      <c r="E131" s="30"/>
+      <c r="F131" s="30"/>
+      <c r="G131" s="30"/>
+      <c r="H131" s="30"/>
     </row>
     <row r="132" spans="2:8">
-      <c r="B132" s="25"/>
-      <c r="C132" s="25"/>
-      <c r="D132" s="25"/>
-      <c r="E132" s="25"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="25"/>
-      <c r="H132" s="25"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="30"/>
+      <c r="D132" s="30"/>
+      <c r="E132" s="30"/>
+      <c r="F132" s="30"/>
+      <c r="G132" s="30"/>
+      <c r="H132" s="30"/>
     </row>
     <row r="133" spans="2:8">
-      <c r="B133" s="25"/>
-      <c r="C133" s="25"/>
-      <c r="D133" s="25"/>
-      <c r="E133" s="25"/>
-      <c r="F133" s="25"/>
-      <c r="G133" s="25"/>
-      <c r="H133" s="25"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="30"/>
+      <c r="E133" s="30"/>
+      <c r="F133" s="30"/>
+      <c r="G133" s="30"/>
+      <c r="H133" s="30"/>
     </row>
     <row r="134" spans="2:8">
-      <c r="B134" s="25"/>
-      <c r="C134" s="25"/>
-      <c r="D134" s="25"/>
-      <c r="E134" s="25"/>
-      <c r="F134" s="25"/>
-      <c r="G134" s="25"/>
-      <c r="H134" s="25"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="30"/>
+      <c r="D134" s="30"/>
+      <c r="E134" s="30"/>
+      <c r="F134" s="30"/>
+      <c r="G134" s="30"/>
+      <c r="H134" s="30"/>
     </row>
     <row r="135" spans="2:8">
-      <c r="B135" s="25"/>
-      <c r="C135" s="25"/>
-      <c r="D135" s="25"/>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="30"/>
+      <c r="D135" s="30"/>
+      <c r="E135" s="30"/>
+      <c r="F135" s="30"/>
+      <c r="G135" s="30"/>
+      <c r="H135" s="30"/>
     </row>
     <row r="136" spans="2:8">
-      <c r="B136" s="25"/>
-      <c r="C136" s="25"/>
-      <c r="D136" s="25"/>
-      <c r="E136" s="25"/>
-      <c r="F136" s="25"/>
-      <c r="G136" s="25"/>
-      <c r="H136" s="25"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="30"/>
+      <c r="E136" s="30"/>
+      <c r="F136" s="30"/>
+      <c r="G136" s="30"/>
+      <c r="H136" s="30"/>
     </row>
     <row r="137" spans="2:8">
-      <c r="B137" s="25"/>
-      <c r="C137" s="25"/>
-      <c r="D137" s="25"/>
-      <c r="E137" s="25"/>
-      <c r="F137" s="25"/>
-      <c r="G137" s="25"/>
-      <c r="H137" s="25"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+      <c r="D137" s="30"/>
+      <c r="E137" s="30"/>
+      <c r="F137" s="30"/>
+      <c r="G137" s="30"/>
+      <c r="H137" s="30"/>
     </row>
     <row r="138" spans="2:8">
-      <c r="B138" s="25"/>
-      <c r="C138" s="25"/>
-      <c r="D138" s="25"/>
-      <c r="E138" s="25"/>
-      <c r="F138" s="25"/>
-      <c r="G138" s="25"/>
-      <c r="H138" s="25"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="30"/>
+      <c r="D138" s="30"/>
+      <c r="E138" s="30"/>
+      <c r="F138" s="30"/>
+      <c r="G138" s="30"/>
+      <c r="H138" s="30"/>
     </row>
     <row r="139" spans="2:8">
-      <c r="B139" s="25"/>
-      <c r="C139" s="25"/>
-      <c r="D139" s="25"/>
-      <c r="E139" s="25"/>
-      <c r="F139" s="25"/>
-      <c r="G139" s="25"/>
-      <c r="H139" s="25"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="30"/>
+      <c r="D139" s="30"/>
+      <c r="E139" s="30"/>
+      <c r="F139" s="30"/>
+      <c r="G139" s="30"/>
+      <c r="H139" s="30"/>
     </row>
     <row r="140" spans="2:8">
-      <c r="B140" s="25"/>
-      <c r="C140" s="25"/>
-      <c r="D140" s="25"/>
-      <c r="E140" s="25"/>
-      <c r="F140" s="25"/>
-      <c r="G140" s="25"/>
-      <c r="H140" s="25"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="30"/>
+      <c r="E140" s="30"/>
+      <c r="F140" s="30"/>
+      <c r="G140" s="30"/>
+      <c r="H140" s="30"/>
     </row>
     <row r="141" spans="2:8">
-      <c r="B141" s="25"/>
-      <c r="C141" s="25"/>
-      <c r="D141" s="25"/>
-      <c r="E141" s="25"/>
-      <c r="F141" s="25"/>
-      <c r="G141" s="25"/>
-      <c r="H141" s="25"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="30"/>
+      <c r="D141" s="30"/>
+      <c r="E141" s="30"/>
+      <c r="F141" s="30"/>
+      <c r="G141" s="30"/>
+      <c r="H141" s="30"/>
     </row>
     <row r="142" spans="2:8">
-      <c r="B142" s="25"/>
-      <c r="C142" s="25"/>
-      <c r="D142" s="25"/>
-      <c r="E142" s="25"/>
-      <c r="F142" s="25"/>
-      <c r="G142" s="25"/>
-      <c r="H142" s="25"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="30"/>
+      <c r="D142" s="30"/>
+      <c r="E142" s="30"/>
+      <c r="F142" s="30"/>
+      <c r="G142" s="30"/>
+      <c r="H142" s="30"/>
     </row>
     <row r="143" spans="2:8">
-      <c r="B143" s="25"/>
-      <c r="C143" s="25"/>
-      <c r="D143" s="25"/>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+      <c r="D143" s="30"/>
+      <c r="E143" s="30"/>
+      <c r="F143" s="30"/>
+      <c r="G143" s="30"/>
+      <c r="H143" s="30"/>
     </row>
     <row r="144" spans="2:8">
-      <c r="B144" s="25"/>
-      <c r="C144" s="25"/>
-      <c r="D144" s="25"/>
-      <c r="E144" s="25"/>
-      <c r="F144" s="25"/>
-      <c r="G144" s="25"/>
-      <c r="H144" s="25"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="30"/>
+      <c r="E144" s="30"/>
+      <c r="F144" s="30"/>
+      <c r="G144" s="30"/>
+      <c r="H144" s="30"/>
     </row>
     <row r="145" spans="2:8">
-      <c r="B145" s="25"/>
-      <c r="C145" s="25"/>
-      <c r="D145" s="25"/>
-      <c r="E145" s="25"/>
-      <c r="F145" s="25"/>
-      <c r="G145" s="25"/>
-      <c r="H145" s="25"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="30"/>
+      <c r="D145" s="30"/>
+      <c r="E145" s="30"/>
+      <c r="F145" s="30"/>
+      <c r="G145" s="30"/>
+      <c r="H145" s="30"/>
     </row>
     <row r="146" spans="2:8">
-      <c r="B146" s="25"/>
-      <c r="C146" s="25"/>
-      <c r="D146" s="25"/>
-      <c r="E146" s="25"/>
-      <c r="F146" s="25"/>
-      <c r="G146" s="25"/>
-      <c r="H146" s="25"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="30"/>
+      <c r="D146" s="30"/>
+      <c r="E146" s="30"/>
+      <c r="F146" s="30"/>
+      <c r="G146" s="30"/>
+      <c r="H146" s="30"/>
     </row>
     <row r="147" spans="2:8">
-      <c r="B147" s="25"/>
-      <c r="C147" s="25"/>
-      <c r="D147" s="25"/>
-      <c r="E147" s="25"/>
-      <c r="F147" s="25"/>
-      <c r="G147" s="25"/>
-      <c r="H147" s="25"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="30"/>
+      <c r="D147" s="30"/>
+      <c r="E147" s="30"/>
+      <c r="F147" s="30"/>
+      <c r="G147" s="30"/>
+      <c r="H147" s="30"/>
     </row>
     <row r="148" spans="2:8">
-      <c r="B148" s="25"/>
-      <c r="C148" s="25"/>
-      <c r="D148" s="25"/>
-      <c r="E148" s="25"/>
-      <c r="F148" s="25"/>
-      <c r="G148" s="25"/>
-      <c r="H148" s="25"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="30"/>
+      <c r="D148" s="30"/>
+      <c r="E148" s="30"/>
+      <c r="F148" s="30"/>
+      <c r="G148" s="30"/>
+      <c r="H148" s="30"/>
     </row>
     <row r="149" spans="2:8">
-      <c r="B149" s="25"/>
-      <c r="C149" s="25"/>
-      <c r="D149" s="25"/>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25"/>
-      <c r="G149" s="25"/>
-      <c r="H149" s="25"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
+      <c r="D149" s="30"/>
+      <c r="E149" s="30"/>
+      <c r="F149" s="30"/>
+      <c r="G149" s="30"/>
+      <c r="H149" s="30"/>
     </row>
     <row r="150" spans="2:8">
-      <c r="B150" s="25"/>
-      <c r="C150" s="25"/>
-      <c r="D150" s="25"/>
-      <c r="E150" s="25"/>
-      <c r="F150" s="25"/>
-      <c r="G150" s="25"/>
-      <c r="H150" s="25"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="30"/>
+      <c r="D150" s="30"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="30"/>
+      <c r="H150" s="30"/>
     </row>
     <row r="151" spans="2:8">
-      <c r="B151" s="25"/>
-      <c r="C151" s="25"/>
-      <c r="D151" s="25"/>
-      <c r="E151" s="25"/>
-      <c r="F151" s="25"/>
-      <c r="G151" s="25"/>
-      <c r="H151" s="25"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="30"/>
+      <c r="D151" s="30"/>
+      <c r="E151" s="30"/>
+      <c r="F151" s="30"/>
+      <c r="G151" s="30"/>
+      <c r="H151" s="30"/>
     </row>
     <row r="152" spans="2:8">
-      <c r="B152" s="25"/>
-      <c r="C152" s="25"/>
-      <c r="D152" s="25"/>
-      <c r="E152" s="25"/>
-      <c r="F152" s="25"/>
-      <c r="G152" s="25"/>
-      <c r="H152" s="25"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="30"/>
+      <c r="D152" s="30"/>
+      <c r="E152" s="30"/>
+      <c r="F152" s="30"/>
+      <c r="G152" s="30"/>
+      <c r="H152" s="30"/>
     </row>
     <row r="153" spans="2:8">
-      <c r="B153" s="25"/>
-      <c r="C153" s="25"/>
-      <c r="D153" s="25"/>
-      <c r="E153" s="25"/>
-      <c r="F153" s="25"/>
-      <c r="G153" s="25"/>
-      <c r="H153" s="25"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="30"/>
+      <c r="D153" s="30"/>
+      <c r="E153" s="30"/>
+      <c r="F153" s="30"/>
+      <c r="G153" s="30"/>
+      <c r="H153" s="30"/>
     </row>
     <row r="154" spans="2:8">
-      <c r="B154" s="25"/>
-      <c r="C154" s="25"/>
-      <c r="D154" s="25"/>
-      <c r="E154" s="25"/>
-      <c r="F154" s="25"/>
-      <c r="G154" s="25"/>
-      <c r="H154" s="25"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="30"/>
+      <c r="D154" s="30"/>
+      <c r="E154" s="30"/>
+      <c r="F154" s="30"/>
+      <c r="G154" s="30"/>
+      <c r="H154" s="30"/>
     </row>
     <row r="155" spans="2:8">
-      <c r="B155" s="25"/>
-      <c r="C155" s="25"/>
-      <c r="D155" s="25"/>
-      <c r="E155" s="25"/>
-      <c r="F155" s="25"/>
-      <c r="G155" s="25"/>
-      <c r="H155" s="25"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
+      <c r="D155" s="30"/>
+      <c r="E155" s="30"/>
+      <c r="F155" s="30"/>
+      <c r="G155" s="30"/>
+      <c r="H155" s="30"/>
     </row>
     <row r="156" spans="2:8">
-      <c r="B156" s="25"/>
-      <c r="C156" s="25"/>
-      <c r="D156" s="25"/>
-      <c r="E156" s="25"/>
-      <c r="F156" s="25"/>
-      <c r="G156" s="25"/>
-      <c r="H156" s="25"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="30"/>
+      <c r="D156" s="30"/>
+      <c r="E156" s="30"/>
+      <c r="F156" s="30"/>
+      <c r="G156" s="30"/>
+      <c r="H156" s="30"/>
     </row>
     <row r="157" spans="2:8">
-      <c r="B157" s="25"/>
-      <c r="C157" s="25"/>
-      <c r="D157" s="25"/>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="30"/>
+      <c r="D157" s="30"/>
+      <c r="E157" s="30"/>
+      <c r="F157" s="30"/>
+      <c r="G157" s="30"/>
+      <c r="H157" s="30"/>
     </row>
     <row r="158" spans="2:8">
-      <c r="B158" s="25"/>
-      <c r="C158" s="25"/>
-      <c r="D158" s="25"/>
-      <c r="E158" s="25"/>
-      <c r="F158" s="25"/>
-      <c r="G158" s="25"/>
-      <c r="H158" s="25"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="30"/>
+      <c r="D158" s="30"/>
+      <c r="E158" s="30"/>
+      <c r="F158" s="30"/>
+      <c r="G158" s="30"/>
+      <c r="H158" s="30"/>
     </row>
     <row r="159" spans="2:8">
-      <c r="B159" s="25"/>
-      <c r="C159" s="25"/>
-      <c r="D159" s="25"/>
-      <c r="E159" s="25"/>
-      <c r="F159" s="25"/>
-      <c r="G159" s="25"/>
-      <c r="H159" s="25"/>
+      <c r="B159" s="30"/>
+      <c r="C159" s="30"/>
+      <c r="D159" s="30"/>
+      <c r="E159" s="30"/>
+      <c r="F159" s="30"/>
+      <c r="G159" s="30"/>
+      <c r="H159" s="30"/>
     </row>
     <row r="160" spans="2:8">
-      <c r="B160" s="25"/>
-      <c r="C160" s="25"/>
-      <c r="D160" s="25"/>
-      <c r="E160" s="25"/>
-      <c r="F160" s="25"/>
-      <c r="G160" s="25"/>
-      <c r="H160" s="25"/>
+      <c r="B160" s="30"/>
+      <c r="C160" s="30"/>
+      <c r="D160" s="30"/>
+      <c r="E160" s="30"/>
+      <c r="F160" s="30"/>
+      <c r="G160" s="30"/>
+      <c r="H160" s="30"/>
     </row>
     <row r="161" spans="2:8">
-      <c r="B161" s="25"/>
-      <c r="C161" s="25"/>
-      <c r="D161" s="25"/>
-      <c r="E161" s="25"/>
-      <c r="F161" s="25"/>
-      <c r="G161" s="25"/>
-      <c r="H161" s="25"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+      <c r="D161" s="30"/>
+      <c r="E161" s="30"/>
+      <c r="F161" s="30"/>
+      <c r="G161" s="30"/>
+      <c r="H161" s="30"/>
     </row>
     <row r="162" spans="2:8">
-      <c r="B162" s="25"/>
-      <c r="C162" s="25"/>
-      <c r="D162" s="25"/>
-      <c r="E162" s="25"/>
-      <c r="F162" s="25"/>
-      <c r="G162" s="25"/>
-      <c r="H162" s="25"/>
+      <c r="B162" s="30"/>
+      <c r="C162" s="30"/>
+      <c r="D162" s="30"/>
+      <c r="E162" s="30"/>
+      <c r="F162" s="30"/>
+      <c r="G162" s="30"/>
+      <c r="H162" s="30"/>
     </row>
     <row r="163" spans="2:8">
-      <c r="B163" s="25"/>
-      <c r="C163" s="25"/>
-      <c r="D163" s="25"/>
-      <c r="E163" s="25"/>
-      <c r="F163" s="25"/>
-      <c r="G163" s="25"/>
-      <c r="H163" s="25"/>
+      <c r="B163" s="30"/>
+      <c r="C163" s="30"/>
+      <c r="D163" s="30"/>
+      <c r="E163" s="30"/>
+      <c r="F163" s="30"/>
+      <c r="G163" s="30"/>
+      <c r="H163" s="30"/>
     </row>
     <row r="164" spans="2:8">
-      <c r="B164" s="25"/>
-      <c r="C164" s="25"/>
-      <c r="D164" s="25"/>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
+      <c r="B164" s="30"/>
+      <c r="C164" s="30"/>
+      <c r="D164" s="30"/>
+      <c r="E164" s="30"/>
+      <c r="F164" s="30"/>
+      <c r="G164" s="30"/>
+      <c r="H164" s="30"/>
     </row>
     <row r="165" spans="2:8">
-      <c r="B165" s="25"/>
-      <c r="C165" s="25"/>
-      <c r="D165" s="25"/>
-      <c r="E165" s="25"/>
-      <c r="F165" s="25"/>
-      <c r="G165" s="25"/>
-      <c r="H165" s="25"/>
+      <c r="B165" s="30"/>
+      <c r="C165" s="30"/>
+      <c r="D165" s="30"/>
+      <c r="E165" s="30"/>
+      <c r="F165" s="30"/>
+      <c r="G165" s="30"/>
+      <c r="H165" s="30"/>
     </row>
     <row r="166" spans="2:8">
-      <c r="B166" s="25"/>
-      <c r="C166" s="25"/>
-      <c r="D166" s="25"/>
-      <c r="E166" s="25"/>
-      <c r="F166" s="25"/>
-      <c r="G166" s="25"/>
-      <c r="H166" s="25"/>
+      <c r="B166" s="30"/>
+      <c r="C166" s="30"/>
+      <c r="D166" s="30"/>
+      <c r="E166" s="30"/>
+      <c r="F166" s="30"/>
+      <c r="G166" s="30"/>
+      <c r="H166" s="30"/>
     </row>
     <row r="167" spans="2:8">
-      <c r="B167" s="25"/>
-      <c r="C167" s="25"/>
-      <c r="D167" s="25"/>
-      <c r="E167" s="25"/>
-      <c r="F167" s="25"/>
-      <c r="G167" s="25"/>
-      <c r="H167" s="25"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
+      <c r="D167" s="30"/>
+      <c r="E167" s="30"/>
+      <c r="F167" s="30"/>
+      <c r="G167" s="30"/>
+      <c r="H167" s="30"/>
     </row>
     <row r="168" spans="2:8">
-      <c r="B168" s="25"/>
-      <c r="C168" s="25"/>
-      <c r="D168" s="25"/>
-      <c r="E168" s="25"/>
-      <c r="F168" s="25"/>
-      <c r="G168" s="25"/>
-      <c r="H168" s="25"/>
+      <c r="B168" s="30"/>
+      <c r="C168" s="30"/>
+      <c r="D168" s="30"/>
+      <c r="E168" s="30"/>
+      <c r="F168" s="30"/>
+      <c r="G168" s="30"/>
+      <c r="H168" s="30"/>
     </row>
     <row r="169" spans="2:8">
-      <c r="B169" s="25"/>
-      <c r="C169" s="25"/>
-      <c r="D169" s="25"/>
-      <c r="E169" s="25"/>
-      <c r="F169" s="25"/>
-      <c r="G169" s="25"/>
-      <c r="H169" s="25"/>
+      <c r="B169" s="30"/>
+      <c r="C169" s="30"/>
+      <c r="D169" s="30"/>
+      <c r="E169" s="30"/>
+      <c r="F169" s="30"/>
+      <c r="G169" s="30"/>
+      <c r="H169" s="30"/>
     </row>
     <row r="170" spans="2:8">
-      <c r="B170" s="25"/>
-      <c r="C170" s="25"/>
-      <c r="D170" s="25"/>
-      <c r="E170" s="25"/>
-      <c r="F170" s="25"/>
-      <c r="G170" s="25"/>
-      <c r="H170" s="25"/>
+      <c r="B170" s="30"/>
+      <c r="C170" s="30"/>
+      <c r="D170" s="30"/>
+      <c r="E170" s="30"/>
+      <c r="F170" s="30"/>
+      <c r="G170" s="30"/>
+      <c r="H170" s="30"/>
     </row>
     <row r="171" spans="2:8">
-      <c r="B171" s="25"/>
-      <c r="C171" s="25"/>
-      <c r="D171" s="25"/>
-      <c r="E171" s="25"/>
-      <c r="F171" s="25"/>
-      <c r="G171" s="25"/>
-      <c r="H171" s="25"/>
+      <c r="B171" s="30"/>
+      <c r="C171" s="30"/>
+      <c r="D171" s="30"/>
+      <c r="E171" s="30"/>
+      <c r="F171" s="30"/>
+      <c r="G171" s="30"/>
+      <c r="H171" s="30"/>
     </row>
     <row r="172" spans="2:8">
-      <c r="B172" s="25"/>
-      <c r="C172" s="25"/>
-      <c r="D172" s="25"/>
-      <c r="E172" s="25"/>
-      <c r="F172" s="25"/>
-      <c r="G172" s="25"/>
-      <c r="H172" s="25"/>
+      <c r="B172" s="30"/>
+      <c r="C172" s="30"/>
+      <c r="D172" s="30"/>
+      <c r="E172" s="30"/>
+      <c r="F172" s="30"/>
+      <c r="G172" s="30"/>
+      <c r="H172" s="30"/>
     </row>
     <row r="173" spans="2:8">
-      <c r="B173" s="25"/>
-      <c r="C173" s="25"/>
-      <c r="D173" s="25"/>
-      <c r="E173" s="25"/>
-      <c r="F173" s="25"/>
-      <c r="G173" s="25"/>
-      <c r="H173" s="25"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+      <c r="D173" s="30"/>
+      <c r="E173" s="30"/>
+      <c r="F173" s="30"/>
+      <c r="G173" s="30"/>
+      <c r="H173" s="30"/>
     </row>
     <row r="174" spans="2:8">
-      <c r="B174" s="25"/>
-      <c r="C174" s="25"/>
-      <c r="D174" s="25"/>
-      <c r="E174" s="25"/>
-      <c r="F174" s="25"/>
-      <c r="G174" s="25"/>
-      <c r="H174" s="25"/>
+      <c r="B174" s="30"/>
+      <c r="C174" s="30"/>
+      <c r="D174" s="30"/>
+      <c r="E174" s="30"/>
+      <c r="F174" s="30"/>
+      <c r="G174" s="30"/>
+      <c r="H174" s="30"/>
     </row>
     <row r="175" spans="2:8">
-      <c r="B175" s="25"/>
-      <c r="C175" s="25"/>
-      <c r="D175" s="25"/>
-      <c r="E175" s="25"/>
-      <c r="F175" s="25"/>
-      <c r="G175" s="25"/>
-      <c r="H175" s="25"/>
+      <c r="B175" s="30"/>
+      <c r="C175" s="30"/>
+      <c r="D175" s="30"/>
+      <c r="E175" s="30"/>
+      <c r="F175" s="30"/>
+      <c r="G175" s="30"/>
+      <c r="H175" s="30"/>
     </row>
     <row r="176" spans="2:8">
-      <c r="B176" s="25"/>
-      <c r="C176" s="25"/>
-      <c r="D176" s="25"/>
-      <c r="E176" s="25"/>
-      <c r="F176" s="25"/>
-      <c r="G176" s="25"/>
-      <c r="H176" s="25"/>
+      <c r="B176" s="30"/>
+      <c r="C176" s="30"/>
+      <c r="D176" s="30"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="30"/>
+      <c r="G176" s="30"/>
+      <c r="H176" s="30"/>
     </row>
     <row r="177" spans="2:8">
-      <c r="B177" s="25"/>
-      <c r="C177" s="25"/>
-      <c r="D177" s="25"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="25"/>
+      <c r="B177" s="30"/>
+      <c r="C177" s="30"/>
+      <c r="D177" s="30"/>
+      <c r="E177" s="30"/>
+      <c r="F177" s="30"/>
+      <c r="G177" s="30"/>
+      <c r="H177" s="30"/>
     </row>
     <row r="178" spans="2:8">
-      <c r="B178" s="25"/>
-      <c r="C178" s="25"/>
-      <c r="D178" s="25"/>
-      <c r="E178" s="25"/>
-      <c r="F178" s="25"/>
-      <c r="G178" s="25"/>
-      <c r="H178" s="25"/>
+      <c r="B178" s="30"/>
+      <c r="C178" s="30"/>
+      <c r="D178" s="30"/>
+      <c r="E178" s="30"/>
+      <c r="F178" s="30"/>
+      <c r="G178" s="30"/>
+      <c r="H178" s="30"/>
     </row>
     <row r="179" spans="2:8">
-      <c r="B179" s="25"/>
-      <c r="C179" s="25"/>
-      <c r="D179" s="25"/>
-      <c r="E179" s="25"/>
-      <c r="F179" s="25"/>
-      <c r="G179" s="25"/>
-      <c r="H179" s="25"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
+      <c r="D179" s="30"/>
+      <c r="E179" s="30"/>
+      <c r="F179" s="30"/>
+      <c r="G179" s="30"/>
+      <c r="H179" s="30"/>
     </row>
     <row r="180" spans="2:8">
-      <c r="B180" s="25"/>
-      <c r="C180" s="25"/>
-      <c r="D180" s="25"/>
-      <c r="E180" s="25"/>
-      <c r="F180" s="25"/>
-      <c r="G180" s="25"/>
-      <c r="H180" s="25"/>
+      <c r="B180" s="30"/>
+      <c r="C180" s="30"/>
+      <c r="D180" s="30"/>
+      <c r="E180" s="30"/>
+      <c r="F180" s="30"/>
+      <c r="G180" s="30"/>
+      <c r="H180" s="30"/>
     </row>
     <row r="181" spans="2:8">
-      <c r="B181" s="25"/>
-      <c r="C181" s="25"/>
-      <c r="D181" s="25"/>
-      <c r="E181" s="25"/>
-      <c r="F181" s="25"/>
-      <c r="G181" s="25"/>
-      <c r="H181" s="25"/>
+      <c r="B181" s="30"/>
+      <c r="C181" s="30"/>
+      <c r="D181" s="30"/>
+      <c r="E181" s="30"/>
+      <c r="F181" s="30"/>
+      <c r="G181" s="30"/>
+      <c r="H181" s="30"/>
     </row>
     <row r="182" spans="2:8">
-      <c r="B182" s="25"/>
-      <c r="C182" s="25"/>
-      <c r="D182" s="25"/>
-      <c r="E182" s="25"/>
-      <c r="F182" s="25"/>
-      <c r="G182" s="25"/>
-      <c r="H182" s="25"/>
+      <c r="B182" s="30"/>
+      <c r="C182" s="30"/>
+      <c r="D182" s="30"/>
+      <c r="E182" s="30"/>
+      <c r="F182" s="30"/>
+      <c r="G182" s="30"/>
+      <c r="H182" s="30"/>
     </row>
     <row r="183" spans="2:8">
-      <c r="B183" s="25"/>
-      <c r="C183" s="25"/>
-      <c r="D183" s="25"/>
-      <c r="E183" s="25"/>
-      <c r="F183" s="25"/>
-      <c r="G183" s="25"/>
-      <c r="H183" s="25"/>
+      <c r="B183" s="30"/>
+      <c r="C183" s="30"/>
+      <c r="D183" s="30"/>
+      <c r="E183" s="30"/>
+      <c r="F183" s="30"/>
+      <c r="G183" s="30"/>
+      <c r="H183" s="30"/>
     </row>
     <row r="184" spans="2:8">
-      <c r="B184" s="25"/>
-      <c r="C184" s="25"/>
-      <c r="D184" s="25"/>
-      <c r="E184" s="25"/>
-      <c r="F184" s="25"/>
-      <c r="G184" s="25"/>
-      <c r="H184" s="25"/>
+      <c r="B184" s="30"/>
+      <c r="C184" s="30"/>
+      <c r="D184" s="30"/>
+      <c r="E184" s="30"/>
+      <c r="F184" s="30"/>
+      <c r="G184" s="30"/>
+      <c r="H184" s="30"/>
     </row>
     <row r="185" spans="2:8">
-      <c r="B185" s="25"/>
-      <c r="C185" s="25"/>
-      <c r="D185" s="25"/>
-      <c r="E185" s="25"/>
-      <c r="F185" s="25"/>
-      <c r="G185" s="25"/>
-      <c r="H185" s="25"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
+      <c r="D185" s="30"/>
+      <c r="E185" s="30"/>
+      <c r="F185" s="30"/>
+      <c r="G185" s="30"/>
+      <c r="H185" s="30"/>
     </row>
     <row r="186" spans="2:8">
-      <c r="B186" s="25"/>
-      <c r="C186" s="25"/>
-      <c r="D186" s="25"/>
-      <c r="E186" s="25"/>
-      <c r="F186" s="25"/>
-      <c r="G186" s="25"/>
-      <c r="H186" s="25"/>
+      <c r="B186" s="30"/>
+      <c r="C186" s="30"/>
+      <c r="D186" s="30"/>
+      <c r="E186" s="30"/>
+      <c r="F186" s="30"/>
+      <c r="G186" s="30"/>
+      <c r="H186" s="30"/>
     </row>
     <row r="187" spans="2:8">
-      <c r="B187" s="25"/>
-      <c r="C187" s="25"/>
-      <c r="D187" s="25"/>
-      <c r="E187" s="25"/>
-      <c r="F187" s="25"/>
-      <c r="G187" s="25"/>
-      <c r="H187" s="25"/>
+      <c r="B187" s="30"/>
+      <c r="C187" s="30"/>
+      <c r="D187" s="30"/>
+      <c r="E187" s="30"/>
+      <c r="F187" s="30"/>
+      <c r="G187" s="30"/>
+      <c r="H187" s="30"/>
     </row>
     <row r="188" spans="2:8">
-      <c r="B188" s="25"/>
-      <c r="C188" s="25"/>
-      <c r="D188" s="25"/>
-      <c r="E188" s="25"/>
-      <c r="F188" s="25"/>
-      <c r="G188" s="25"/>
-      <c r="H188" s="25"/>
+      <c r="B188" s="30"/>
+      <c r="C188" s="30"/>
+      <c r="D188" s="30"/>
+      <c r="E188" s="30"/>
+      <c r="F188" s="30"/>
+      <c r="G188" s="30"/>
+      <c r="H188" s="30"/>
     </row>
     <row r="189" spans="2:8">
-      <c r="B189" s="25"/>
-      <c r="C189" s="25"/>
-      <c r="D189" s="25"/>
-      <c r="E189" s="25"/>
-      <c r="F189" s="25"/>
-      <c r="G189" s="25"/>
-      <c r="H189" s="25"/>
+      <c r="B189" s="30"/>
+      <c r="C189" s="30"/>
+      <c r="D189" s="30"/>
+      <c r="E189" s="30"/>
+      <c r="F189" s="30"/>
+      <c r="G189" s="30"/>
+      <c r="H189" s="30"/>
     </row>
     <row r="190" spans="2:8">
-      <c r="B190" s="25"/>
-      <c r="C190" s="25"/>
-      <c r="D190" s="25"/>
-      <c r="E190" s="25"/>
-      <c r="F190" s="25"/>
-      <c r="G190" s="25"/>
-      <c r="H190" s="25"/>
+      <c r="B190" s="30"/>
+      <c r="C190" s="30"/>
+      <c r="D190" s="30"/>
+      <c r="E190" s="30"/>
+      <c r="F190" s="30"/>
+      <c r="G190" s="30"/>
+      <c r="H190" s="30"/>
     </row>
     <row r="191" spans="2:8">
-      <c r="B191" s="25"/>
-      <c r="C191" s="25"/>
-      <c r="D191" s="25"/>
-      <c r="E191" s="25"/>
-      <c r="F191" s="25"/>
-      <c r="G191" s="25"/>
-      <c r="H191" s="25"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
+      <c r="D191" s="30"/>
+      <c r="E191" s="30"/>
+      <c r="F191" s="30"/>
+      <c r="G191" s="30"/>
+      <c r="H191" s="30"/>
     </row>
     <row r="192" spans="2:8">
-      <c r="B192" s="25"/>
-      <c r="C192" s="25"/>
-      <c r="D192" s="25"/>
-      <c r="E192" s="25"/>
-      <c r="F192" s="25"/>
-      <c r="G192" s="25"/>
-      <c r="H192" s="25"/>
+      <c r="B192" s="30"/>
+      <c r="C192" s="30"/>
+      <c r="D192" s="30"/>
+      <c r="E192" s="30"/>
+      <c r="F192" s="30"/>
+      <c r="G192" s="30"/>
+      <c r="H192" s="30"/>
     </row>
     <row r="193" spans="2:8">
-      <c r="B193" s="25"/>
-      <c r="C193" s="25"/>
-      <c r="D193" s="25"/>
-      <c r="E193" s="25"/>
-      <c r="F193" s="25"/>
-      <c r="G193" s="25"/>
-      <c r="H193" s="25"/>
+      <c r="B193" s="30"/>
+      <c r="C193" s="30"/>
+      <c r="D193" s="30"/>
+      <c r="E193" s="30"/>
+      <c r="F193" s="30"/>
+      <c r="G193" s="30"/>
+      <c r="H193" s="30"/>
     </row>
     <row r="194" spans="2:8">
-      <c r="B194" s="25"/>
-      <c r="C194" s="25"/>
-      <c r="D194" s="25"/>
-      <c r="E194" s="25"/>
-      <c r="F194" s="25"/>
-      <c r="G194" s="25"/>
-      <c r="H194" s="25"/>
+      <c r="B194" s="30"/>
+      <c r="C194" s="30"/>
+      <c r="D194" s="30"/>
+      <c r="E194" s="30"/>
+      <c r="F194" s="30"/>
+      <c r="G194" s="30"/>
+      <c r="H194" s="30"/>
     </row>
     <row r="195" spans="2:8">
-      <c r="B195" s="25"/>
-      <c r="C195" s="25"/>
-      <c r="D195" s="25"/>
-      <c r="E195" s="25"/>
-      <c r="F195" s="25"/>
-      <c r="G195" s="25"/>
-      <c r="H195" s="25"/>
+      <c r="B195" s="30"/>
+      <c r="C195" s="30"/>
+      <c r="D195" s="30"/>
+      <c r="E195" s="30"/>
+      <c r="F195" s="30"/>
+      <c r="G195" s="30"/>
+      <c r="H195" s="30"/>
     </row>
     <row r="196" spans="2:8">
-      <c r="B196" s="25"/>
-      <c r="C196" s="25"/>
-      <c r="D196" s="25"/>
-      <c r="E196" s="25"/>
-      <c r="F196" s="25"/>
-      <c r="G196" s="25"/>
-      <c r="H196" s="25"/>
+      <c r="B196" s="30"/>
+      <c r="C196" s="30"/>
+      <c r="D196" s="30"/>
+      <c r="E196" s="30"/>
+      <c r="F196" s="30"/>
+      <c r="G196" s="30"/>
+      <c r="H196" s="30"/>
     </row>
     <row r="197" spans="2:8">
-      <c r="B197" s="25"/>
-      <c r="C197" s="25"/>
-      <c r="D197" s="25"/>
-      <c r="E197" s="25"/>
-      <c r="F197" s="25"/>
-      <c r="G197" s="25"/>
-      <c r="H197" s="25"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
+      <c r="D197" s="30"/>
+      <c r="E197" s="30"/>
+      <c r="F197" s="30"/>
+      <c r="G197" s="30"/>
+      <c r="H197" s="30"/>
     </row>
     <row r="198" spans="2:8">
-      <c r="B198" s="25"/>
-      <c r="C198" s="25"/>
-      <c r="D198" s="25"/>
-      <c r="E198" s="25"/>
-      <c r="F198" s="25"/>
-      <c r="G198" s="25"/>
-      <c r="H198" s="25"/>
+      <c r="B198" s="30"/>
+      <c r="C198" s="30"/>
+      <c r="D198" s="30"/>
+      <c r="E198" s="30"/>
+      <c r="F198" s="30"/>
+      <c r="G198" s="30"/>
+      <c r="H198" s="30"/>
     </row>
     <row r="199" spans="2:8">
-      <c r="B199" s="25"/>
-      <c r="C199" s="25"/>
-      <c r="D199" s="25"/>
-      <c r="E199" s="25"/>
-      <c r="F199" s="25"/>
-      <c r="G199" s="25"/>
-      <c r="H199" s="25"/>
+      <c r="B199" s="30"/>
+      <c r="C199" s="30"/>
+      <c r="D199" s="30"/>
+      <c r="E199" s="30"/>
+      <c r="F199" s="30"/>
+      <c r="G199" s="30"/>
+      <c r="H199" s="30"/>
     </row>
     <row r="200" spans="2:8">
-      <c r="B200" s="25"/>
-      <c r="C200" s="25"/>
-      <c r="D200" s="25"/>
-      <c r="E200" s="25"/>
-      <c r="F200" s="25"/>
-      <c r="G200" s="25"/>
-      <c r="H200" s="25"/>
+      <c r="B200" s="30"/>
+      <c r="C200" s="30"/>
+      <c r="D200" s="30"/>
+      <c r="E200" s="30"/>
+      <c r="F200" s="30"/>
+      <c r="G200" s="30"/>
+      <c r="H200" s="30"/>
     </row>
     <row r="201" spans="2:8">
-      <c r="B201" s="25"/>
-      <c r="C201" s="25"/>
-      <c r="D201" s="25"/>
-      <c r="E201" s="25"/>
-      <c r="F201" s="25"/>
-      <c r="G201" s="25"/>
-      <c r="H201" s="25"/>
+      <c r="B201" s="30"/>
+      <c r="C201" s="30"/>
+      <c r="D201" s="30"/>
+      <c r="E201" s="30"/>
+      <c r="F201" s="30"/>
+      <c r="G201" s="30"/>
+      <c r="H201" s="30"/>
     </row>
     <row r="202" spans="2:8">
-      <c r="B202" s="25"/>
-      <c r="C202" s="25"/>
-      <c r="D202" s="25"/>
-      <c r="E202" s="25"/>
-      <c r="F202" s="25"/>
-      <c r="G202" s="25"/>
-      <c r="H202" s="25"/>
+      <c r="B202" s="30"/>
+      <c r="C202" s="30"/>
+      <c r="D202" s="30"/>
+      <c r="E202" s="30"/>
+      <c r="F202" s="30"/>
+      <c r="G202" s="30"/>
+      <c r="H202" s="30"/>
     </row>
     <row r="203" spans="2:8">
-      <c r="B203" s="25"/>
-      <c r="C203" s="25"/>
-      <c r="D203" s="25"/>
-      <c r="E203" s="25"/>
-      <c r="F203" s="25"/>
-      <c r="G203" s="25"/>
-      <c r="H203" s="25"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
+      <c r="D203" s="30"/>
+      <c r="E203" s="30"/>
+      <c r="F203" s="30"/>
+      <c r="G203" s="30"/>
+      <c r="H203" s="30"/>
     </row>
     <row r="204" spans="2:8">
-      <c r="B204" s="25"/>
-      <c r="C204" s="25"/>
-      <c r="D204" s="25"/>
-      <c r="E204" s="25"/>
-      <c r="F204" s="25"/>
-      <c r="G204" s="25"/>
-      <c r="H204" s="25"/>
+      <c r="B204" s="30"/>
+      <c r="C204" s="30"/>
+      <c r="D204" s="30"/>
+      <c r="E204" s="30"/>
+      <c r="F204" s="30"/>
+      <c r="G204" s="30"/>
+      <c r="H204" s="30"/>
     </row>
     <row r="205" spans="2:8">
-      <c r="B205" s="25"/>
-      <c r="C205" s="25"/>
-      <c r="D205" s="25"/>
-      <c r="E205" s="25"/>
-      <c r="F205" s="25"/>
-      <c r="G205" s="25"/>
-      <c r="H205" s="25"/>
+      <c r="B205" s="30"/>
+      <c r="C205" s="30"/>
+      <c r="D205" s="30"/>
+      <c r="E205" s="30"/>
+      <c r="F205" s="30"/>
+      <c r="G205" s="30"/>
+      <c r="H205" s="30"/>
     </row>
     <row r="206" spans="2:8">
-      <c r="B206" s="25"/>
-      <c r="C206" s="25"/>
-      <c r="D206" s="25"/>
-      <c r="E206" s="25"/>
-      <c r="F206" s="25"/>
-      <c r="G206" s="25"/>
-      <c r="H206" s="25"/>
+      <c r="B206" s="30"/>
+      <c r="C206" s="30"/>
+      <c r="D206" s="30"/>
+      <c r="E206" s="30"/>
+      <c r="F206" s="30"/>
+      <c r="G206" s="30"/>
+      <c r="H206" s="30"/>
     </row>
     <row r="207" spans="2:8">
-      <c r="B207" s="25"/>
-      <c r="C207" s="25"/>
-      <c r="D207" s="25"/>
-      <c r="E207" s="25"/>
-      <c r="F207" s="25"/>
-      <c r="G207" s="25"/>
-      <c r="H207" s="25"/>
+      <c r="B207" s="30"/>
+      <c r="C207" s="30"/>
+      <c r="D207" s="30"/>
+      <c r="E207" s="30"/>
+      <c r="F207" s="30"/>
+      <c r="G207" s="30"/>
+      <c r="H207" s="30"/>
     </row>
     <row r="208" spans="2:8">
-      <c r="B208" s="25"/>
-      <c r="C208" s="25"/>
-      <c r="D208" s="25"/>
-      <c r="E208" s="25"/>
-      <c r="F208" s="25"/>
-      <c r="G208" s="25"/>
-      <c r="H208" s="25"/>
+      <c r="B208" s="30"/>
+      <c r="C208" s="30"/>
+      <c r="D208" s="30"/>
+      <c r="E208" s="30"/>
+      <c r="F208" s="30"/>
+      <c r="G208" s="30"/>
+      <c r="H208" s="30"/>
     </row>
     <row r="209" spans="2:8">
-      <c r="B209" s="25"/>
-      <c r="C209" s="25"/>
-      <c r="D209" s="25"/>
-      <c r="E209" s="25"/>
-      <c r="F209" s="25"/>
-      <c r="G209" s="25"/>
-      <c r="H209" s="25"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
+      <c r="D209" s="30"/>
+      <c r="E209" s="30"/>
+      <c r="F209" s="30"/>
+      <c r="G209" s="30"/>
+      <c r="H209" s="30"/>
     </row>
     <row r="210" spans="2:8">
-      <c r="B210" s="25"/>
-      <c r="C210" s="25"/>
-      <c r="D210" s="25"/>
-      <c r="E210" s="25"/>
-      <c r="F210" s="25"/>
-      <c r="G210" s="25"/>
-      <c r="H210" s="25"/>
+      <c r="B210" s="30"/>
+      <c r="C210" s="30"/>
+      <c r="D210" s="30"/>
+      <c r="E210" s="30"/>
+      <c r="F210" s="30"/>
+      <c r="G210" s="30"/>
+      <c r="H210" s="30"/>
     </row>
     <row r="211" spans="2:8">
-      <c r="B211" s="25"/>
-      <c r="C211" s="25"/>
-      <c r="D211" s="25"/>
-      <c r="E211" s="25"/>
-      <c r="F211" s="25"/>
-      <c r="G211" s="25"/>
-      <c r="H211" s="25"/>
+      <c r="B211" s="30"/>
+      <c r="C211" s="30"/>
+      <c r="D211" s="30"/>
+      <c r="E211" s="30"/>
+      <c r="F211" s="30"/>
+      <c r="G211" s="30"/>
+      <c r="H211" s="30"/>
     </row>
     <row r="212" spans="2:8">
-      <c r="B212" s="25"/>
-      <c r="C212" s="25"/>
-      <c r="D212" s="25"/>
-      <c r="E212" s="25"/>
-      <c r="F212" s="25"/>
-      <c r="G212" s="25"/>
-      <c r="H212" s="25"/>
+      <c r="B212" s="30"/>
+      <c r="C212" s="30"/>
+      <c r="D212" s="30"/>
+      <c r="E212" s="30"/>
+      <c r="F212" s="30"/>
+      <c r="G212" s="30"/>
+      <c r="H212" s="30"/>
     </row>
     <row r="213" spans="2:8">
-      <c r="B213" s="25"/>
-      <c r="C213" s="25"/>
-      <c r="D213" s="25"/>
-      <c r="E213" s="25"/>
-      <c r="F213" s="25"/>
-      <c r="G213" s="25"/>
-      <c r="H213" s="25"/>
+      <c r="B213" s="30"/>
+      <c r="C213" s="30"/>
+      <c r="D213" s="30"/>
+      <c r="E213" s="30"/>
+      <c r="F213" s="30"/>
+      <c r="G213" s="30"/>
+      <c r="H213" s="30"/>
     </row>
     <row r="214" spans="2:8">
-      <c r="B214" s="25"/>
-      <c r="C214" s="25"/>
-      <c r="D214" s="25"/>
-      <c r="E214" s="25"/>
-      <c r="F214" s="25"/>
-      <c r="G214" s="25"/>
-      <c r="H214" s="25"/>
+      <c r="B214" s="30"/>
+      <c r="C214" s="30"/>
+      <c r="D214" s="30"/>
+      <c r="E214" s="30"/>
+      <c r="F214" s="30"/>
+      <c r="G214" s="30"/>
+      <c r="H214" s="30"/>
     </row>
     <row r="215" spans="2:8">
-      <c r="B215" s="25"/>
-      <c r="C215" s="25"/>
-      <c r="D215" s="25"/>
-      <c r="E215" s="25"/>
-      <c r="F215" s="25"/>
-      <c r="G215" s="25"/>
-      <c r="H215" s="25"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
+      <c r="D215" s="30"/>
+      <c r="E215" s="30"/>
+      <c r="F215" s="30"/>
+      <c r="G215" s="30"/>
+      <c r="H215" s="30"/>
     </row>
     <row r="216" spans="2:8">
-      <c r="B216" s="25"/>
-      <c r="C216" s="25"/>
-      <c r="D216" s="25"/>
-      <c r="E216" s="25"/>
-      <c r="F216" s="25"/>
-      <c r="G216" s="25"/>
-      <c r="H216" s="25"/>
+      <c r="B216" s="30"/>
+      <c r="C216" s="30"/>
+      <c r="D216" s="30"/>
+      <c r="E216" s="30"/>
+      <c r="F216" s="30"/>
+      <c r="G216" s="30"/>
+      <c r="H216" s="30"/>
     </row>
     <row r="217" spans="2:8">
-      <c r="B217" s="25"/>
-      <c r="C217" s="25"/>
-      <c r="D217" s="25"/>
-      <c r="E217" s="25"/>
-      <c r="F217" s="25"/>
-      <c r="G217" s="25"/>
-      <c r="H217" s="25"/>
+      <c r="B217" s="30"/>
+      <c r="C217" s="30"/>
+      <c r="D217" s="30"/>
+      <c r="E217" s="30"/>
+      <c r="F217" s="30"/>
+      <c r="G217" s="30"/>
+      <c r="H217" s="30"/>
     </row>
     <row r="218" spans="2:8">
-      <c r="B218" s="25"/>
-      <c r="C218" s="25"/>
-      <c r="D218" s="25"/>
-      <c r="E218" s="25"/>
-      <c r="F218" s="25"/>
-      <c r="G218" s="25"/>
-      <c r="H218" s="25"/>
+      <c r="B218" s="30"/>
+      <c r="C218" s="30"/>
+      <c r="D218" s="30"/>
+      <c r="E218" s="30"/>
+      <c r="F218" s="30"/>
+      <c r="G218" s="30"/>
+      <c r="H218" s="30"/>
     </row>
     <row r="219" spans="2:8">
-      <c r="B219" s="25"/>
-      <c r="C219" s="25"/>
-      <c r="D219" s="25"/>
-      <c r="E219" s="25"/>
-      <c r="F219" s="25"/>
-      <c r="G219" s="25"/>
-      <c r="H219" s="25"/>
+      <c r="B219" s="30"/>
+      <c r="C219" s="30"/>
+      <c r="D219" s="30"/>
+      <c r="E219" s="30"/>
+      <c r="F219" s="30"/>
+      <c r="G219" s="30"/>
+      <c r="H219" s="30"/>
     </row>
     <row r="220" spans="2:8">
-      <c r="B220" s="25"/>
-      <c r="C220" s="25"/>
-      <c r="D220" s="25"/>
-      <c r="E220" s="25"/>
-      <c r="F220" s="25"/>
-      <c r="G220" s="25"/>
-      <c r="H220" s="25"/>
+      <c r="B220" s="30"/>
+      <c r="C220" s="30"/>
+      <c r="D220" s="30"/>
+      <c r="E220" s="30"/>
+      <c r="F220" s="30"/>
+      <c r="G220" s="30"/>
+      <c r="H220" s="30"/>
     </row>
     <row r="221" spans="2:8">
-      <c r="B221" s="25"/>
-      <c r="C221" s="25"/>
-      <c r="D221" s="25"/>
-      <c r="E221" s="25"/>
-      <c r="F221" s="25"/>
-      <c r="G221" s="25"/>
-      <c r="H221" s="25"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+      <c r="D221" s="30"/>
+      <c r="E221" s="30"/>
+      <c r="F221" s="30"/>
+      <c r="G221" s="30"/>
+      <c r="H221" s="30"/>
     </row>
     <row r="222" spans="2:8">
-      <c r="B222" s="25"/>
-      <c r="C222" s="25"/>
-      <c r="D222" s="25"/>
-      <c r="E222" s="25"/>
-      <c r="F222" s="25"/>
-      <c r="G222" s="25"/>
-      <c r="H222" s="25"/>
+      <c r="B222" s="30"/>
+      <c r="C222" s="30"/>
+      <c r="D222" s="30"/>
+      <c r="E222" s="30"/>
+      <c r="F222" s="30"/>
+      <c r="G222" s="30"/>
+      <c r="H222" s="30"/>
     </row>
     <row r="223" spans="2:8">
-      <c r="B223" s="25"/>
-      <c r="C223" s="25"/>
-      <c r="D223" s="25"/>
-      <c r="E223" s="25"/>
-      <c r="F223" s="25"/>
-      <c r="G223" s="25"/>
-      <c r="H223" s="25"/>
+      <c r="B223" s="30"/>
+      <c r="C223" s="30"/>
+      <c r="D223" s="30"/>
+      <c r="E223" s="30"/>
+      <c r="F223" s="30"/>
+      <c r="G223" s="30"/>
+      <c r="H223" s="30"/>
     </row>
     <row r="224" spans="2:8">
-      <c r="B224" s="25"/>
-      <c r="C224" s="25"/>
-      <c r="D224" s="25"/>
-      <c r="E224" s="25"/>
-      <c r="F224" s="25"/>
-      <c r="G224" s="25"/>
-      <c r="H224" s="25"/>
+      <c r="B224" s="30"/>
+      <c r="C224" s="30"/>
+      <c r="D224" s="30"/>
+      <c r="E224" s="30"/>
+      <c r="F224" s="30"/>
+      <c r="G224" s="30"/>
+      <c r="H224" s="30"/>
     </row>
     <row r="225" spans="2:8">
-      <c r="B225" s="25"/>
-      <c r="C225" s="25"/>
-      <c r="D225" s="25"/>
-      <c r="E225" s="25"/>
-      <c r="F225" s="25"/>
-      <c r="G225" s="25"/>
-      <c r="H225" s="25"/>
+      <c r="B225" s="30"/>
+      <c r="C225" s="30"/>
+      <c r="D225" s="30"/>
+      <c r="E225" s="30"/>
+      <c r="F225" s="30"/>
+      <c r="G225" s="30"/>
+      <c r="H225" s="30"/>
     </row>
     <row r="226" spans="2:8">
-      <c r="B226" s="25"/>
-      <c r="C226" s="25"/>
-      <c r="D226" s="25"/>
-      <c r="E226" s="25"/>
-      <c r="F226" s="25"/>
-      <c r="G226" s="25"/>
-      <c r="H226" s="25"/>
+      <c r="B226" s="30"/>
+      <c r="C226" s="30"/>
+      <c r="D226" s="30"/>
+      <c r="E226" s="30"/>
+      <c r="F226" s="30"/>
+      <c r="G226" s="30"/>
+      <c r="H226" s="30"/>
     </row>
     <row r="228" spans="2:8" s="23" customFormat="1" ht="7.15" customHeight="1"/>
     <row r="230" spans="2:8">
@@ -7333,6 +12279,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f5cf7016-d570-4e66-bed5-9c66354e4d60">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006416C8A108E61840AFB84A4598B73E55" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b1d8d0092a91b491fa162699921cd7b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f5cf7016-d570-4e66-bed5-9c66354e4d60" xmlns:ns3="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc769dae83c42ca581dc5110a4ef7ce3" ns2:_="" ns3:_="">
     <xsd:import namespace="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
@@ -7539,27 +12505,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f5cf7016-d570-4e66-bed5-9c66354e4d60">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B672EAD0-EA6C-460E-95E6-5BDD1102E907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7929c02-2ff7-4e2f-b3f4-5d7437463a37"/>
+    <ds:schemaRef ds:uri="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11299929-15DA-49D6-A514-2A8A25D7CF50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7576,23 +12541,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B672EAD0-EA6C-460E-95E6-5BDD1102E907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7929c02-2ff7-4e2f-b3f4-5d7437463a37"/>
-    <ds:schemaRef ds:uri="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
+++ b/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.valadez\Documents\Repositorios\rocket-benchtest-stand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Engineering\01 Repos\rocket-benchtest-stand\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0623EDE7-AC27-4517-962E-9E622229157C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21195" windowHeight="8085" activeTab="4"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
     <sheet name="Truss design 2.0" sheetId="8" r:id="rId5"/>
     <sheet name="Instrumentation" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,14 +41,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="238">
   <si>
     <t>(Materials selection in mechanical design, pp 12)</t>
   </si>
@@ -852,11 +853,14 @@
   <si>
     <t>Large member</t>
   </si>
+  <si>
+    <t>Welding joint analysis</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -1230,7 +1234,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1328,6 +1332,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
@@ -1404,6 +1413,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="7"/>
@@ -1480,6 +1494,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="8"/>
@@ -1556,6 +1575,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="9"/>
@@ -1632,6 +1656,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="0"/>
@@ -1702,6 +1731,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1772,6 +1806,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1842,6 +1881,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1912,6 +1956,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -1982,6 +2031,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-DB50-479D-9043-705D97A14E93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2164,7 +2218,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2262,6 +2316,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F9EA-4D43-95B3-60586230201B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2332,6 +2391,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F9EA-4D43-95B3-60586230201B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2402,6 +2466,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F9EA-4D43-95B3-60586230201B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -2472,6 +2541,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-F9EA-4D43-95B3-60586230201B}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2654,7 +2728,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2752,6 +2826,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
@@ -2828,6 +2907,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="7"/>
@@ -2904,6 +2988,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="8"/>
@@ -2980,6 +3069,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="9"/>
@@ -3056,6 +3150,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="0"/>
@@ -3126,6 +3225,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -3196,6 +3300,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -3266,6 +3375,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -3336,6 +3450,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -3406,6 +3525,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="10"/>
@@ -3482,6 +3606,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="11"/>
@@ -3558,6 +3687,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="12"/>
@@ -3637,6 +3771,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="13"/>
@@ -3716,6 +3855,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-4CAF-4C5C-9F21-EBC0F6EC3924}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -5586,7 +5730,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5635,7 +5779,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5679,7 +5823,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5728,7 +5872,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5772,7 +5916,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5821,7 +5965,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5882,7 +6026,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5945,7 +6089,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -5975,7 +6125,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -6005,7 +6161,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -6045,7 +6207,7 @@
         <xdr:cNvPr id="6145" name="AutoShape 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6458,16 +6620,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:R27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:18" ht="15" thickBot="1">
       <c r="I2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="15.75" thickBot="1">
+    <row r="3" spans="2:18" ht="15" thickBot="1">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -6539,7 +6701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="15">
+    <row r="12" spans="2:18">
       <c r="B12" t="s">
         <v>19</v>
       </c>
@@ -6630,7 +6792,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R6" r:id="rId1"/>
+    <hyperlink ref="R6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -6639,18 +6801,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N121"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="4"/>
-    <col min="2" max="2" width="18.875" style="4" customWidth="1"/>
-    <col min="3" max="10" width="8.875" style="4"/>
+    <col min="1" max="1" width="8.90625" style="4"/>
+    <col min="2" max="2" width="18.90625" style="4" customWidth="1"/>
+    <col min="3" max="10" width="8.90625" style="4"/>
     <col min="11" max="11" width="18" style="4" customWidth="1"/>
-    <col min="12" max="12" width="23.25" style="4" customWidth="1"/>
-    <col min="13" max="13" width="8.875" style="4"/>
-    <col min="14" max="14" width="30.875" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="4"/>
+    <col min="12" max="12" width="23.26953125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.90625" style="4"/>
+    <col min="14" max="14" width="30.90625" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15" thickBot="1"/>
@@ -6716,7 +6878,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1">
+    <row r="5" spans="2:14" ht="15" thickBot="1">
       <c r="B5" s="10"/>
       <c r="C5" s="11">
         <v>18</v>
@@ -6737,7 +6899,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15">
+    <row r="6" spans="2:14">
       <c r="B6" s="6" t="s">
         <v>52</v>
       </c>
@@ -6766,7 +6928,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="15.75" thickBot="1">
+    <row r="7" spans="2:14" ht="15" thickBot="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>18</v>
@@ -6787,7 +6949,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="15">
+    <row r="8" spans="2:14">
       <c r="B8" s="6" t="s">
         <v>55</v>
       </c>
@@ -6810,7 +6972,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="15">
+    <row r="9" spans="2:14">
       <c r="B9" s="13"/>
       <c r="C9" s="11">
         <v>18</v>
@@ -6831,7 +6993,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="15">
+    <row r="10" spans="2:14">
       <c r="B10" s="13"/>
       <c r="C10" s="11">
         <v>16</v>
@@ -6852,7 +7014,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="15.75" thickBot="1">
+    <row r="11" spans="2:14" ht="15" thickBot="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>14</v>
@@ -6873,7 +7035,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="15">
+    <row r="12" spans="2:14">
       <c r="B12" s="6" t="s">
         <v>56</v>
       </c>
@@ -6896,7 +7058,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="15">
+    <row r="13" spans="2:14">
       <c r="B13" s="13"/>
       <c r="C13" s="11">
         <v>18</v>
@@ -6917,7 +7079,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="15">
+    <row r="14" spans="2:14">
       <c r="B14" s="13"/>
       <c r="C14" s="11">
         <v>16</v>
@@ -6938,7 +7100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="15">
+    <row r="15" spans="2:14">
       <c r="B15" s="13"/>
       <c r="C15" s="11">
         <v>14</v>
@@ -6959,7 +7121,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="15">
+    <row r="16" spans="2:14">
       <c r="B16" s="13"/>
       <c r="C16" s="11">
         <v>13</v>
@@ -6980,7 +7142,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15">
+    <row r="17" spans="2:8">
       <c r="B17" s="13"/>
       <c r="C17" s="11">
         <v>12</v>
@@ -7001,7 +7163,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15">
+    <row r="18" spans="2:8">
       <c r="B18" s="13"/>
       <c r="C18" s="11">
         <v>11</v>
@@ -7022,7 +7184,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15.75" thickBot="1">
+    <row r="19" spans="2:8" ht="15" thickBot="1">
       <c r="B19" s="10"/>
       <c r="C19" s="11">
         <v>10</v>
@@ -7043,7 +7205,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15">
+    <row r="20" spans="2:8">
       <c r="B20" s="6" t="s">
         <v>58</v>
       </c>
@@ -7066,7 +7228,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15">
+    <row r="21" spans="2:8">
       <c r="B21" s="13"/>
       <c r="C21" s="11">
         <v>18</v>
@@ -7087,7 +7249,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15">
+    <row r="22" spans="2:8">
       <c r="B22" s="13"/>
       <c r="C22" s="11">
         <v>16</v>
@@ -7108,7 +7270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="15">
+    <row r="23" spans="2:8">
       <c r="B23" s="13"/>
       <c r="C23" s="11">
         <v>14</v>
@@ -7129,7 +7291,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="15.75" thickBot="1">
+    <row r="24" spans="2:8" ht="15" thickBot="1">
       <c r="B24" s="10"/>
       <c r="C24" s="11">
         <v>12</v>
@@ -7150,7 +7312,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="15">
+    <row r="25" spans="2:8">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -7173,7 +7335,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15">
+    <row r="26" spans="2:8">
       <c r="B26" s="13"/>
       <c r="C26" s="11">
         <v>18</v>
@@ -7194,7 +7356,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15">
+    <row r="27" spans="2:8">
       <c r="B27" s="13"/>
       <c r="C27" s="11">
         <v>16</v>
@@ -7215,7 +7377,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15">
+    <row r="28" spans="2:8">
       <c r="B28" s="13"/>
       <c r="C28" s="11">
         <v>14</v>
@@ -7236,7 +7398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="15">
+    <row r="29" spans="2:8">
       <c r="B29" s="13"/>
       <c r="C29" s="11">
         <v>12</v>
@@ -7257,7 +7419,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15.75" thickBot="1">
+    <row r="30" spans="2:8" ht="15" thickBot="1">
       <c r="B30" s="10"/>
       <c r="C30" s="11">
         <v>9</v>
@@ -7278,7 +7440,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="15">
+    <row r="31" spans="2:8">
       <c r="B31" s="6" t="s">
         <v>60</v>
       </c>
@@ -7301,7 +7463,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="15">
+    <row r="32" spans="2:8">
       <c r="B32" s="13"/>
       <c r="C32" s="11">
         <v>14</v>
@@ -7322,7 +7484,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="15">
+    <row r="33" spans="2:9">
       <c r="B33" s="13"/>
       <c r="C33" s="11">
         <v>12</v>
@@ -7343,7 +7505,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="15">
+    <row r="34" spans="2:9">
       <c r="B34" s="13"/>
       <c r="C34" s="11">
         <v>10</v>
@@ -7364,7 +7526,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="15.75" thickBot="1">
+    <row r="35" spans="2:9" ht="15" thickBot="1">
       <c r="B35" s="10"/>
       <c r="C35" s="11">
         <v>9</v>
@@ -7385,7 +7547,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="15">
+    <row r="36" spans="2:9">
       <c r="B36" s="6" t="s">
         <v>61</v>
       </c>
@@ -7408,7 +7570,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="15">
+    <row r="37" spans="2:9">
       <c r="B37" s="13"/>
       <c r="C37" s="11">
         <v>11</v>
@@ -7429,7 +7591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="15">
+    <row r="38" spans="2:9">
       <c r="B38" s="13"/>
       <c r="C38" s="11">
         <v>7</v>
@@ -7450,7 +7612,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="15.75" thickBot="1">
+    <row r="39" spans="2:9" ht="15" thickBot="1">
       <c r="B39" s="10"/>
       <c r="C39" s="11" t="s">
         <v>62</v>
@@ -7471,7 +7633,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="15">
+    <row r="40" spans="2:9">
       <c r="B40" s="6" t="s">
         <v>63</v>
       </c>
@@ -7494,7 +7656,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="28.5">
+    <row r="41" spans="2:9" ht="29">
       <c r="B41" s="13"/>
       <c r="C41" s="11">
         <v>11</v>
@@ -7515,7 +7677,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="15">
+    <row r="42" spans="2:9">
       <c r="B42" s="13"/>
       <c r="C42" s="11">
         <v>9</v>
@@ -7536,7 +7698,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="15">
+    <row r="43" spans="2:9">
       <c r="B43" s="13"/>
       <c r="C43" s="11">
         <v>7</v>
@@ -7557,7 +7719,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="29.25" thickBot="1">
+    <row r="44" spans="2:9" ht="29.5" thickBot="1">
       <c r="B44" s="10"/>
       <c r="C44" s="11" t="s">
         <v>62</v>
@@ -7578,7 +7740,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="15">
+    <row r="45" spans="2:9">
       <c r="B45" s="6" t="s">
         <v>65</v>
       </c>
@@ -7601,7 +7763,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="15.75" thickBot="1">
+    <row r="46" spans="2:9" ht="15" thickBot="1">
       <c r="B46" s="13"/>
       <c r="C46" s="11">
         <v>9</v>
@@ -7622,7 +7784,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="15.75" thickBot="1">
+    <row r="47" spans="2:9" ht="15" thickBot="1">
       <c r="B47" s="13"/>
       <c r="C47" s="11">
         <v>7</v>
@@ -7644,7 +7806,7 @@
       </c>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="2:9" ht="29.25" thickBot="1">
+    <row r="48" spans="2:9" ht="29.5" thickBot="1">
       <c r="B48" s="10"/>
       <c r="C48" s="11" t="s">
         <v>62</v>
@@ -7665,7 +7827,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="15">
+    <row r="49" spans="2:9">
       <c r="B49" s="6" t="s">
         <v>67</v>
       </c>
@@ -7688,7 +7850,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="29.25" thickBot="1">
+    <row r="50" spans="2:9" ht="29.5" thickBot="1">
       <c r="B50" s="13"/>
       <c r="C50" s="11" t="s">
         <v>68</v>
@@ -7709,7 +7871,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="15.75" thickBot="1">
+    <row r="51" spans="2:9" ht="15" thickBot="1">
       <c r="B51" s="13"/>
       <c r="C51" s="11">
         <v>9</v>
@@ -7731,7 +7893,7 @@
       </c>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="2:9" ht="28.5">
+    <row r="52" spans="2:9" ht="29">
       <c r="B52" s="13"/>
       <c r="C52" s="11" t="s">
         <v>69</v>
@@ -7752,7 +7914,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="29.25" thickBot="1">
+    <row r="53" spans="2:9" ht="29.5" thickBot="1">
       <c r="B53" s="10"/>
       <c r="C53" s="11" t="s">
         <v>62</v>
@@ -7773,7 +7935,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="28.5">
+    <row r="54" spans="2:9" ht="29">
       <c r="B54" s="6" t="s">
         <v>70</v>
       </c>
@@ -7796,7 +7958,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="28.5">
+    <row r="55" spans="2:9" ht="29">
       <c r="B55" s="13"/>
       <c r="C55" s="11" t="s">
         <v>69</v>
@@ -7817,7 +7979,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="29.25" thickBot="1">
+    <row r="56" spans="2:9" ht="29.5" thickBot="1">
       <c r="B56" s="10"/>
       <c r="C56" s="14" t="s">
         <v>62</v>
@@ -7862,7 +8024,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="15.75" thickBot="1">
+    <row r="60" spans="2:9" ht="15" thickBot="1">
       <c r="B60" s="10" t="s">
         <v>72</v>
       </c>
@@ -7885,7 +8047,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="2:9" ht="15">
+    <row r="61" spans="2:9">
       <c r="B61" s="6" t="s">
         <v>73</v>
       </c>
@@ -7908,7 +8070,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="15.75" thickBot="1">
+    <row r="62" spans="2:9" ht="15" thickBot="1">
       <c r="B62" s="10"/>
       <c r="C62" s="11">
         <v>18</v>
@@ -7929,7 +8091,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="15">
+    <row r="63" spans="2:9">
       <c r="B63" s="6" t="s">
         <v>74</v>
       </c>
@@ -7952,7 +8114,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="15.75" thickBot="1">
+    <row r="64" spans="2:9" ht="15" thickBot="1">
       <c r="B64" s="10"/>
       <c r="C64" s="11">
         <v>18</v>
@@ -7973,7 +8135,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="15">
+    <row r="65" spans="2:8">
       <c r="B65" s="6" t="s">
         <v>75</v>
       </c>
@@ -7996,7 +8158,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="15">
+    <row r="66" spans="2:8">
       <c r="B66" s="13"/>
       <c r="C66" s="11">
         <v>18</v>
@@ -8017,7 +8179,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="15">
+    <row r="67" spans="2:8">
       <c r="B67" s="13"/>
       <c r="C67" s="11">
         <v>16</v>
@@ -8038,7 +8200,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="15">
+    <row r="68" spans="2:8">
       <c r="B68" s="13"/>
       <c r="C68" s="11">
         <v>14</v>
@@ -8059,7 +8221,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="15.75" thickBot="1">
+    <row r="69" spans="2:8" ht="15" thickBot="1">
       <c r="B69" s="10"/>
       <c r="C69" s="11">
         <v>11</v>
@@ -8080,7 +8242,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="2:8" ht="15">
+    <row r="70" spans="2:8">
       <c r="B70" s="6" t="s">
         <v>76</v>
       </c>
@@ -8103,7 +8265,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="15.75" thickBot="1">
+    <row r="71" spans="2:8" ht="15" thickBot="1">
       <c r="B71" s="10"/>
       <c r="C71" s="11">
         <v>18</v>
@@ -8124,7 +8286,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="15">
+    <row r="72" spans="2:8">
       <c r="B72" s="6" t="s">
         <v>77</v>
       </c>
@@ -8147,7 +8309,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="15">
+    <row r="73" spans="2:8">
       <c r="B73" s="13"/>
       <c r="C73" s="11">
         <v>18</v>
@@ -8168,7 +8330,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="15">
+    <row r="74" spans="2:8">
       <c r="B74" s="13"/>
       <c r="C74" s="11">
         <v>14</v>
@@ -8189,7 +8351,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="15.75" thickBot="1">
+    <row r="75" spans="2:8" ht="15" thickBot="1">
       <c r="B75" s="10"/>
       <c r="C75" s="11">
         <v>11</v>
@@ -8210,7 +8372,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="15">
+    <row r="76" spans="2:8">
       <c r="B76" s="6" t="s">
         <v>78</v>
       </c>
@@ -8233,7 +8395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="15.75" thickBot="1">
+    <row r="77" spans="2:8" ht="15" thickBot="1">
       <c r="B77" s="10"/>
       <c r="C77" s="11">
         <v>18</v>
@@ -8254,7 +8416,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="2:8" ht="15">
+    <row r="78" spans="2:8">
       <c r="B78" s="6" t="s">
         <v>79</v>
       </c>
@@ -8277,7 +8439,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="15">
+    <row r="79" spans="2:8">
       <c r="B79" s="13"/>
       <c r="C79" s="11">
         <v>18</v>
@@ -8298,7 +8460,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="15.75" thickBot="1">
+    <row r="80" spans="2:8" ht="15" thickBot="1">
       <c r="B80" s="10"/>
       <c r="C80" s="11">
         <v>14</v>
@@ -8319,7 +8481,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="15.75" thickBot="1">
+    <row r="81" spans="2:8" ht="15" thickBot="1">
       <c r="B81" s="17" t="s">
         <v>81</v>
       </c>
@@ -8342,7 +8504,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="15">
+    <row r="82" spans="2:8">
       <c r="B82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8365,7 +8527,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="15">
+    <row r="83" spans="2:8">
       <c r="B83" s="13"/>
       <c r="C83" s="11">
         <v>16</v>
@@ -8386,7 +8548,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="15">
+    <row r="84" spans="2:8">
       <c r="B84" s="13"/>
       <c r="C84" s="11">
         <v>14</v>
@@ -8407,7 +8569,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="15">
+    <row r="85" spans="2:8">
       <c r="B85" s="13"/>
       <c r="C85" s="11">
         <v>11</v>
@@ -8428,7 +8590,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15.75" thickBot="1">
+    <row r="86" spans="2:8" ht="15" thickBot="1">
       <c r="B86" s="10"/>
       <c r="C86" s="11">
         <v>10</v>
@@ -8446,7 +8608,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15">
+    <row r="87" spans="2:8">
       <c r="B87" s="6" t="s">
         <v>83</v>
       </c>
@@ -8469,7 +8631,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15">
+    <row r="88" spans="2:8">
       <c r="B88" s="13"/>
       <c r="C88" s="11">
         <v>18</v>
@@ -8490,7 +8652,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15">
+    <row r="89" spans="2:8">
       <c r="B89" s="13"/>
       <c r="C89" s="11">
         <v>14</v>
@@ -8511,7 +8673,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="90" spans="2:8" ht="15.75" thickBot="1">
+    <row r="90" spans="2:8" ht="15" thickBot="1">
       <c r="B90" s="10"/>
       <c r="C90" s="11">
         <v>11</v>
@@ -8532,7 +8694,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="15">
+    <row r="91" spans="2:8">
       <c r="B91" s="6" t="s">
         <v>84</v>
       </c>
@@ -8555,7 +8717,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="15">
+    <row r="92" spans="2:8">
       <c r="B92" s="13"/>
       <c r="C92" s="11">
         <v>11</v>
@@ -8576,7 +8738,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="15">
+    <row r="93" spans="2:8">
       <c r="B93" s="13"/>
       <c r="C93" s="11">
         <v>10</v>
@@ -8597,7 +8759,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="15">
+    <row r="94" spans="2:8">
       <c r="B94" s="13"/>
       <c r="C94" s="11">
         <v>7</v>
@@ -8618,7 +8780,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="15.75" thickBot="1">
+    <row r="95" spans="2:8" ht="15" thickBot="1">
       <c r="B95" s="10"/>
       <c r="C95" s="11" t="s">
         <v>62</v>
@@ -8639,7 +8801,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="15.75" thickBot="1">
+    <row r="96" spans="2:8" ht="15" thickBot="1">
       <c r="B96" s="17" t="s">
         <v>85</v>
       </c>
@@ -8662,7 +8824,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="15">
+    <row r="97" spans="2:8">
       <c r="B97" s="6" t="s">
         <v>86</v>
       </c>
@@ -8685,7 +8847,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="98" spans="2:8" ht="15">
+    <row r="98" spans="2:8">
       <c r="B98" s="13"/>
       <c r="C98" s="11">
         <v>11</v>
@@ -8706,7 +8868,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="15">
+    <row r="99" spans="2:8">
       <c r="B99" s="13"/>
       <c r="C99" s="11">
         <v>9</v>
@@ -8727,7 +8889,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="15">
+    <row r="100" spans="2:8">
       <c r="B100" s="13"/>
       <c r="C100" s="11">
         <v>7</v>
@@ -8748,7 +8910,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="29.25" thickBot="1">
+    <row r="101" spans="2:8" ht="29.5" thickBot="1">
       <c r="B101" s="10"/>
       <c r="C101" s="11" t="s">
         <v>62</v>
@@ -8769,7 +8931,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="2:8" ht="15">
+    <row r="102" spans="2:8">
       <c r="B102" s="6" t="s">
         <v>87</v>
       </c>
@@ -8792,7 +8954,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="15">
+    <row r="103" spans="2:8">
       <c r="B103" s="13"/>
       <c r="C103" s="11">
         <v>11</v>
@@ -8813,7 +8975,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="28.5">
+    <row r="104" spans="2:8" ht="29">
       <c r="B104" s="13"/>
       <c r="C104" s="11">
         <v>9</v>
@@ -8834,7 +8996,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="105" spans="2:8" ht="15">
+    <row r="105" spans="2:8">
       <c r="B105" s="13"/>
       <c r="C105" s="11">
         <v>7</v>
@@ -8855,7 +9017,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="2:8" ht="29.25" thickBot="1">
+    <row r="106" spans="2:8" ht="29.5" thickBot="1">
       <c r="B106" s="10"/>
       <c r="C106" s="11" t="s">
         <v>62</v>
@@ -8876,7 +9038,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="2:8" ht="15">
+    <row r="107" spans="2:8">
       <c r="B107" s="6" t="s">
         <v>88</v>
       </c>
@@ -8899,7 +9061,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="2:8" ht="15.75" thickBot="1">
+    <row r="108" spans="2:8" ht="15" thickBot="1">
       <c r="B108" s="10"/>
       <c r="C108" s="11">
         <v>7</v>
@@ -8920,7 +9082,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="15">
+    <row r="109" spans="2:8">
       <c r="B109" s="6" t="s">
         <v>89</v>
       </c>
@@ -8943,7 +9105,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="28.5">
+    <row r="110" spans="2:8" ht="29">
       <c r="B110" s="13"/>
       <c r="C110" s="11" t="s">
         <v>68</v>
@@ -8964,7 +9126,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="111" spans="2:8" ht="28.5">
+    <row r="111" spans="2:8" ht="29">
       <c r="B111" s="13"/>
       <c r="C111" s="11" t="s">
         <v>69</v>
@@ -8985,7 +9147,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="2:8" ht="29.25" thickBot="1">
+    <row r="112" spans="2:8" ht="29.5" thickBot="1">
       <c r="B112" s="10"/>
       <c r="C112" s="11" t="s">
         <v>62</v>
@@ -9006,7 +9168,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="2:8" ht="15">
+    <row r="113" spans="2:8">
       <c r="B113" s="6" t="s">
         <v>90</v>
       </c>
@@ -9029,7 +9191,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="114" spans="2:8" ht="28.5">
+    <row r="114" spans="2:8" ht="29">
       <c r="B114" s="13"/>
       <c r="C114" s="11" t="s">
         <v>68</v>
@@ -9050,7 +9212,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="115" spans="2:8" ht="28.5">
+    <row r="115" spans="2:8" ht="29">
       <c r="B115" s="13"/>
       <c r="C115" s="11" t="s">
         <v>69</v>
@@ -9071,7 +9233,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="2:8" ht="29.25" thickBot="1">
+    <row r="116" spans="2:8" ht="29.5" thickBot="1">
       <c r="B116" s="10"/>
       <c r="C116" s="11" t="s">
         <v>62</v>
@@ -9092,7 +9254,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" spans="2:8" ht="28.5">
+    <row r="117" spans="2:8" ht="29">
       <c r="B117" s="6" t="s">
         <v>91</v>
       </c>
@@ -9115,7 +9277,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="118" spans="2:8" ht="28.5">
+    <row r="118" spans="2:8" ht="29">
       <c r="B118" s="13"/>
       <c r="C118" s="11" t="s">
         <v>69</v>
@@ -9136,7 +9298,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="2:8" ht="29.25" thickBot="1">
+    <row r="119" spans="2:8" ht="29.5" thickBot="1">
       <c r="B119" s="10"/>
       <c r="C119" s="11" t="s">
         <v>62</v>
@@ -9157,7 +9319,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="120" spans="2:8" ht="15">
+    <row r="120" spans="2:8">
       <c r="B120" s="6" t="s">
         <v>92</v>
       </c>
@@ -9180,7 +9342,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="2:8" ht="15.75" thickBot="1">
+    <row r="121" spans="2:8" ht="15" thickBot="1">
       <c r="B121" s="10"/>
       <c r="C121" s="14" t="s">
         <v>69</v>
@@ -9206,9 +9368,9 @@
     <mergeCell ref="K3:L3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1"/>
-    <hyperlink ref="N4" r:id="rId2" display="https://www.nan-steel.com/news/astm-a500-grade-b.html"/>
-    <hyperlink ref="L6" r:id="rId3" display="https://www.fortacero.com/cat_ptr/"/>
+    <hyperlink ref="L4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="N4" r:id="rId2" display="https://www.nan-steel.com/news/astm-a500-grade-b.html" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="L6" r:id="rId3" display="https://www.fortacero.com/cat_ptr/" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
@@ -9216,9 +9378,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B24:J75"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B24:J79"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="24" spans="2:10">
       <c r="B24" t="s">
@@ -9543,6 +9705,12 @@
     <row r="75" spans="2:3">
       <c r="B75" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" s="23" customFormat="1" ht="4" customHeight="1"/>
+    <row r="79" spans="2:3">
+      <c r="B79" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -9552,9 +9720,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:W36"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="13:19">
       <c r="M2" t="s">
@@ -9786,11 +9954,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:F38"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1"/>
@@ -9903,7 +10071,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="28.5">
+    <row r="14" spans="2:6" ht="29">
       <c r="B14" s="24" t="s">
         <v>234</v>
       </c>
@@ -10224,9 +10392,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:J231"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="3" spans="2:10">
       <c r="B3" t="s">
@@ -12268,10 +12436,10 @@
     <mergeCell ref="B6:H226"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" display="https://es.aliexpress.com/item/1005006070642588.html?spm=a2g0o.detail.1000023.7.6731h1Sth1St9k&amp;gatewayAdapt=glo2esp"/>
-    <hyperlink ref="J7" r:id="rId2" display="https://es.aliexpress.com/item/1005006236153559.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.10.42b5Hp0XHp0XEL&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40000.327270.0&amp;scm_id=1007.40000.327270.0&amp;scm-url=1007.40000.327270.0&amp;pvid=8e8df423-9348-430e-bd8a-ef2b74523ad3&amp;_t=gps-id:pcDetailTopMoreOtherSeller,scm-url:1007.40000.327270.0,pvid:8e8df423-9348-430e-bd8a-ef2b74523ad3,tpp_buckets:668%232846%238115%232000&amp;pdp_npi=4%40dis%21MXN%211440.14%211440.14%21%21%21580.00%21580.00%21%402101c80217210782867234885e2967%2112000036407770943%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A&amp;search_p4p_id=202407151418067686820644873943000265_9"/>
-    <hyperlink ref="J9" r:id="rId3" display="https://es.aliexpress.com/item/1005006732452379.html?spm=a2g0o.detail.pcDetailBottomMoreOtherSeller.7.1a3d4wrx4wrxGR&amp;gps-id=pcDetailBottomMoreOtherSeller&amp;scm=1007.40000.326746.0&amp;scm_id=1007.40000.326746.0&amp;scm-url=1007.40000.326746.0&amp;pvid=b897bdac-172d-4dcc-83a0-454806878ae4&amp;_t=gps-id:pcDetailBottomMoreOtherSeller,scm-url:1007.40000.326746.0,pvid:b897bdac-172d-4dcc-83a0-454806878ae4,tpp_buckets:668%232846%238115%23870&amp;pdp_npi=4%40dis%21MXN%211253.72%21674.56%21%21%21504.92%21271.67%21%402101dee017210836143727304e969f%2112000038120783793%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailBottomMoreOtherSeller%7Cquery_from%3A"/>
-    <hyperlink ref="B231" r:id="rId4" display="https://www.amazon.com.mx/Conversi%C3%B3n-Anal%C3%B3gico-Adquisici%C3%B3n-Precisi%C3%B3n-Anal%C3%B3gicas/dp/B099KR3ZH2/ref=sr_1_4_sspa?__mk_es_MX=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=2ZSLGVRH28XV4&amp;dib=eyJ2IjoiMSJ9.4G6WaOCAu0novMMLXdnrGg.WiLun_ccVPpdns00fxZXsuGMPfwrG2LR9eMn6e7xYY4&amp;dib_tag=se&amp;keywords=adc+high+sps&amp;qid=1739164832&amp;sprefix=adc+high+sps%2Caps%2C118&amp;sr=8-4-spons&amp;ufe=app_do%3Aamzn1.fos.45030d3a-91a9-4303-890a-776dee9077c1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9tdGY&amp;psc=1"/>
+    <hyperlink ref="B4" r:id="rId1" display="https://es.aliexpress.com/item/1005006070642588.html?spm=a2g0o.detail.1000023.7.6731h1Sth1St9k&amp;gatewayAdapt=glo2esp" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="J7" r:id="rId2" display="https://es.aliexpress.com/item/1005006236153559.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.10.42b5Hp0XHp0XEL&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40000.327270.0&amp;scm_id=1007.40000.327270.0&amp;scm-url=1007.40000.327270.0&amp;pvid=8e8df423-9348-430e-bd8a-ef2b74523ad3&amp;_t=gps-id:pcDetailTopMoreOtherSeller,scm-url:1007.40000.327270.0,pvid:8e8df423-9348-430e-bd8a-ef2b74523ad3,tpp_buckets:668%232846%238115%232000&amp;pdp_npi=4%40dis%21MXN%211440.14%211440.14%21%21%21580.00%21580.00%21%402101c80217210782867234885e2967%2112000036407770943%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A&amp;search_p4p_id=202407151418067686820644873943000265_9" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="J9" r:id="rId3" display="https://es.aliexpress.com/item/1005006732452379.html?spm=a2g0o.detail.pcDetailBottomMoreOtherSeller.7.1a3d4wrx4wrxGR&amp;gps-id=pcDetailBottomMoreOtherSeller&amp;scm=1007.40000.326746.0&amp;scm_id=1007.40000.326746.0&amp;scm-url=1007.40000.326746.0&amp;pvid=b897bdac-172d-4dcc-83a0-454806878ae4&amp;_t=gps-id:pcDetailBottomMoreOtherSeller,scm-url:1007.40000.326746.0,pvid:b897bdac-172d-4dcc-83a0-454806878ae4,tpp_buckets:668%232846%238115%23870&amp;pdp_npi=4%40dis%21MXN%211253.72%21674.56%21%21%21504.92%21271.67%21%402101dee017210836143727304e969f%2112000038120783793%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailBottomMoreOtherSeller%7Cquery_from%3A" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="B231" r:id="rId4" display="https://www.amazon.com.mx/Conversi%C3%B3n-Anal%C3%B3gico-Adquisici%C3%B3n-Precisi%C3%B3n-Anal%C3%B3gicas/dp/B099KR3ZH2/ref=sr_1_4_sspa?__mk_es_MX=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=2ZSLGVRH28XV4&amp;dib=eyJ2IjoiMSJ9.4G6WaOCAu0novMMLXdnrGg.WiLun_ccVPpdns00fxZXsuGMPfwrG2LR9eMn6e7xYY4&amp;dib_tag=se&amp;keywords=adc+high+sps&amp;qid=1739164832&amp;sprefix=adc+high+sps%2Caps%2C118&amp;sr=8-4-spons&amp;ufe=app_do%3Aamzn1.fos.45030d3a-91a9-4303-890a-776dee9077c1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9tdGY&amp;psc=1" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId5"/>
@@ -12279,26 +12447,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f5cf7016-d570-4e66-bed5-9c66354e4d60">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006416C8A108E61840AFB84A4598B73E55" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b1d8d0092a91b491fa162699921cd7b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f5cf7016-d570-4e66-bed5-9c66354e4d60" xmlns:ns3="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc769dae83c42ca581dc5110a4ef7ce3" ns2:_="" ns3:_="">
     <xsd:import namespace="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
@@ -12505,26 +12653,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B672EAD0-EA6C-460E-95E6-5BDD1102E907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7929c02-2ff7-4e2f-b3f4-5d7437463a37"/>
-    <ds:schemaRef ds:uri="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f5cf7016-d570-4e66-bed5-9c66354e4d60">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11299929-15DA-49D6-A514-2A8A25D7CF50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12541,4 +12690,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B672EAD0-EA6C-460E-95E6-5BDD1102E907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7929c02-2ff7-4e2f-b3f4-5d7437463a37"/>
+    <ds:schemaRef ds:uri="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
+++ b/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
@@ -1991,11 +1991,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-1316492864"/>
-        <c:axId val="-1316504832"/>
+        <c:axId val="2081233776"/>
+        <c:axId val="2081242480"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-1316492864"/>
+        <c:axId val="2081233776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2052,12 +2052,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1316504832"/>
+        <c:crossAx val="2081242480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-1316504832"/>
+        <c:axId val="2081242480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2114,7 +2114,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1316492864"/>
+        <c:crossAx val="2081233776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2481,11 +2481,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-1390972832"/>
-        <c:axId val="-1390973920"/>
+        <c:axId val="2081243024"/>
+        <c:axId val="2081232688"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-1390972832"/>
+        <c:axId val="2081243024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2542,12 +2542,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1390973920"/>
+        <c:crossAx val="2081232688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-1390973920"/>
+        <c:axId val="2081232688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2604,7 +2604,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1390972832"/>
+        <c:crossAx val="2081243024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3725,11 +3725,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-1316492320"/>
-        <c:axId val="-1316501024"/>
+        <c:axId val="2081227792"/>
+        <c:axId val="2081232144"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-1316492320"/>
+        <c:axId val="2081227792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3786,12 +3786,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1316501024"/>
+        <c:crossAx val="2081232144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-1316501024"/>
+        <c:axId val="2081232144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="150"/>
@@ -3849,7 +3849,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1316492320"/>
+        <c:crossAx val="2081227792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5586,7 +5586,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5635,7 +5635,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5679,7 +5679,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5728,7 +5728,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5772,7 +5772,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5821,7 +5821,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5882,7 +5882,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6045,7 +6045,7 @@
         <xdr:cNvPr id="6145" name="AutoShape 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12279,26 +12279,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f5cf7016-d570-4e66-bed5-9c66354e4d60">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006416C8A108E61840AFB84A4598B73E55" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b1d8d0092a91b491fa162699921cd7b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f5cf7016-d570-4e66-bed5-9c66354e4d60" xmlns:ns3="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc769dae83c42ca581dc5110a4ef7ce3" ns2:_="" ns3:_="">
     <xsd:import namespace="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
@@ -12505,26 +12485,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B672EAD0-EA6C-460E-95E6-5BDD1102E907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7929c02-2ff7-4e2f-b3f4-5d7437463a37"/>
-    <ds:schemaRef ds:uri="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7929c02-2ff7-4e2f-b3f4-5d7437463a37" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f5cf7016-d570-4e66-bed5-9c66354e4d60">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11299929-15DA-49D6-A514-2A8A25D7CF50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12541,4 +12522,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2573117B-6260-4644-A359-931F1507CA1F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B672EAD0-EA6C-460E-95E6-5BDD1102E907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7929c02-2ff7-4e2f-b3f4-5d7437463a37"/>
+    <ds:schemaRef ds:uri="f5cf7016-d570-4e66-bed5-9c66354e4d60"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
+++ b/PROPULSION HRD-01 Diseño de banco de pruebas Maria Rev.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.valadez\Documents\Repositorios\rocket-benchtest-stand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Engineering\01 Repos\rocket-benchtest-stand\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD53ED89-8375-4D3C-8535-EABCF08BD973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21195" windowHeight="8085" activeTab="4"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
     <sheet name="Truss design 2.0" sheetId="8" r:id="rId5"/>
     <sheet name="Instrumentation" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,14 +41,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="277">
   <si>
     <t>(Materials selection in mechanical design, pp 12)</t>
   </si>
@@ -852,11 +853,131 @@
   <si>
     <t>Large member</t>
   </si>
+  <si>
+    <t>Dimensiones de caja de banco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimensiones de plano de banco </t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>viga</t>
+  </si>
+  <si>
+    <t>ranura</t>
+  </si>
+  <si>
+    <t>r1</t>
+  </si>
+  <si>
+    <t>r0</t>
+  </si>
+  <si>
+    <t>Dimensionamiento de "a"</t>
+  </si>
+  <si>
+    <t>1. Nuestro motor</t>
+  </si>
+  <si>
+    <t>30cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. motores h </t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. motores i </t>
+  </si>
+  <si>
+    <t>4. jota</t>
+  </si>
+  <si>
+    <t>5. ka</t>
+  </si>
+  <si>
+    <t>a tiene que ser min de 72.8 cm</t>
+  </si>
+  <si>
+    <t>dimension "b" f(diametro)</t>
+  </si>
+  <si>
+    <t>35mm</t>
+  </si>
+  <si>
+    <t>la dimension b min es de 98 mm</t>
+  </si>
+  <si>
+    <t>que b tiene que ser 2b</t>
+  </si>
+  <si>
+    <t>b puede ser 3 el min de b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la dimension "c" depende de las simulaciones </t>
+  </si>
+  <si>
+    <t>1 probar la sim con el empuje mas grande (motor K) y ver dos casos</t>
+  </si>
+  <si>
+    <t>con la viga de c</t>
+  </si>
+  <si>
+    <t>sin la viga de c</t>
+  </si>
+  <si>
+    <t>si hay un cambio muy notorio, se deja la viga y se juega con la distancia donde se solda</t>
+  </si>
+  <si>
+    <t>Dimension de "B" es f(diametro)</t>
+  </si>
+  <si>
+    <t>tomando los datos de abajo:</t>
+  </si>
+  <si>
+    <t>la dimension "B" debe ser min 98</t>
+  </si>
+  <si>
+    <t>la dimension "B" puede ser 2*B anterior</t>
+  </si>
+  <si>
+    <t>la dimension de "C" = "b"</t>
+  </si>
+  <si>
+    <t>Dimension de "A"</t>
+  </si>
+  <si>
+    <t>la dimension de "A" depende del largo de la viga empotrada la "azul"</t>
+  </si>
+  <si>
+    <t>Dimension "VIGA"</t>
+  </si>
+  <si>
+    <t>simulacion y analisis teorico</t>
+  </si>
+  <si>
+    <t>ranura depende de que tanto se va mover</t>
+  </si>
+  <si>
+    <t>r1 y r0 dependen de donde se va localizar esa ranura</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -1230,7 +1351,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1328,6 +1449,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
@@ -1404,6 +1530,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="7"/>
@@ -1480,6 +1611,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="8"/>
@@ -1556,6 +1692,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="9"/>
@@ -1632,6 +1773,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="0"/>
@@ -1702,6 +1848,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1772,6 +1923,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1842,6 +1998,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1912,6 +2073,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -1982,6 +2148,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-AB38-45D8-8EB3-449F58622633}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2164,7 +2335,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2262,6 +2433,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2B36-43BE-8D49-39F4B712C7A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2332,6 +2508,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2B36-43BE-8D49-39F4B712C7A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2402,6 +2583,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2B36-43BE-8D49-39F4B712C7A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -2472,6 +2658,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2B36-43BE-8D49-39F4B712C7A2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2654,7 +2845,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2752,6 +2943,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
@@ -2828,6 +3024,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="7"/>
@@ -2904,6 +3105,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="8"/>
@@ -2980,6 +3186,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="9"/>
@@ -3056,6 +3267,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="0"/>
@@ -3126,6 +3342,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -3196,6 +3417,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -3266,6 +3492,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -3336,6 +3567,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -3406,6 +3642,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="10"/>
@@ -3482,6 +3723,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="11"/>
@@ -3558,6 +3804,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="12"/>
@@ -3637,6 +3888,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="13"/>
@@ -3716,6 +3972,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-08C3-4BF9-B16D-726E57013EE2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -5586,7 +5847,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5684C3C5-DAA1-0FFD-42E3-3D5DF59271BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5635,7 +5896,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{896B3375-9C92-1B6B-758A-EA72BB08F586}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5679,7 +5940,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA22387-73AB-26F5-3C1D-5737F039543F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5728,7 +5989,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8E8793-F09C-DBBC-8F68-AB2AB1330A6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5772,7 +6033,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED8B252A-7486-70B0-AC76-61C6891FB4D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5821,7 +6082,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4DA1F8-A635-4E4C-9C97-10B5703E0C0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5882,7 +6143,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401281D1-570F-B0E7-290B-B831A7033209}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5945,7 +6206,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -5975,7 +6242,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -6005,7 +6278,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -6020,6 +6299,124 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>224118</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>165215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>21758</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>25401</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0404C6AC-173C-3B58-5D4D-5C3EE1820960}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3182471" y="10071215"/>
+          <a:ext cx="2860581" cy="1914598"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>293281</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>71361</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>144540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC70CF29-4FED-493B-871E-3598FC43B9CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3251634" y="8038353"/>
+          <a:ext cx="2841021" cy="1825422"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:shade val="85000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="88900" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="55000" dist="18000" dir="5400000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="40000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="twoPt" dir="t">
+            <a:rot lat="0" lon="0" rev="7200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="25400" h="19050"/>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6045,7 +6442,7 @@
         <xdr:cNvPr id="6145" name="AutoShape 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF56B6D-0E4C-76D3-7C78-C253C736FF53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6458,16 +6855,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:R27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:18" ht="15" thickBot="1">
       <c r="I2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="15.75" thickBot="1">
+    <row r="3" spans="2:18" ht="15" thickBot="1">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -6539,7 +6936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="15">
+    <row r="12" spans="2:18">
       <c r="B12" t="s">
         <v>19</v>
       </c>
@@ -6630,7 +7027,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R6" r:id="rId1"/>
+    <hyperlink ref="R6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -6639,18 +7036,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:N121"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="4"/>
-    <col min="2" max="2" width="18.875" style="4" customWidth="1"/>
-    <col min="3" max="10" width="8.875" style="4"/>
+    <col min="1" max="1" width="8.90625" style="4"/>
+    <col min="2" max="2" width="18.90625" style="4" customWidth="1"/>
+    <col min="3" max="10" width="8.90625" style="4"/>
     <col min="11" max="11" width="18" style="4" customWidth="1"/>
-    <col min="12" max="12" width="23.25" style="4" customWidth="1"/>
-    <col min="13" max="13" width="8.875" style="4"/>
-    <col min="14" max="14" width="30.875" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="4"/>
+    <col min="12" max="12" width="23.26953125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.90625" style="4"/>
+    <col min="14" max="14" width="30.90625" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15" thickBot="1"/>
@@ -6716,7 +7113,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1">
+    <row r="5" spans="2:14" ht="15" thickBot="1">
       <c r="B5" s="10"/>
       <c r="C5" s="11">
         <v>18</v>
@@ -6737,7 +7134,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15">
+    <row r="6" spans="2:14">
       <c r="B6" s="6" t="s">
         <v>52</v>
       </c>
@@ -6766,7 +7163,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="15.75" thickBot="1">
+    <row r="7" spans="2:14" ht="15" thickBot="1">
       <c r="B7" s="10"/>
       <c r="C7" s="11">
         <v>18</v>
@@ -6787,7 +7184,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="15">
+    <row r="8" spans="2:14">
       <c r="B8" s="6" t="s">
         <v>55</v>
       </c>
@@ -6810,7 +7207,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="15">
+    <row r="9" spans="2:14">
       <c r="B9" s="13"/>
       <c r="C9" s="11">
         <v>18</v>
@@ -6831,7 +7228,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="15">
+    <row r="10" spans="2:14">
       <c r="B10" s="13"/>
       <c r="C10" s="11">
         <v>16</v>
@@ -6852,7 +7249,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="15.75" thickBot="1">
+    <row r="11" spans="2:14" ht="15" thickBot="1">
       <c r="B11" s="10"/>
       <c r="C11" s="11">
         <v>14</v>
@@ -6873,7 +7270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="15">
+    <row r="12" spans="2:14">
       <c r="B12" s="6" t="s">
         <v>56</v>
       </c>
@@ -6896,7 +7293,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="15">
+    <row r="13" spans="2:14">
       <c r="B13" s="13"/>
       <c r="C13" s="11">
         <v>18</v>
@@ -6917,7 +7314,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="15">
+    <row r="14" spans="2:14">
       <c r="B14" s="13"/>
       <c r="C14" s="11">
         <v>16</v>
@@ -6938,7 +7335,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="15">
+    <row r="15" spans="2:14">
       <c r="B15" s="13"/>
       <c r="C15" s="11">
         <v>14</v>
@@ -6959,7 +7356,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="15">
+    <row r="16" spans="2:14">
       <c r="B16" s="13"/>
       <c r="C16" s="11">
         <v>13</v>
@@ -6980,7 +7377,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15">
+    <row r="17" spans="2:8">
       <c r="B17" s="13"/>
       <c r="C17" s="11">
         <v>12</v>
@@ -7001,7 +7398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15">
+    <row r="18" spans="2:8">
       <c r="B18" s="13"/>
       <c r="C18" s="11">
         <v>11</v>
@@ -7022,7 +7419,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15.75" thickBot="1">
+    <row r="19" spans="2:8" ht="15" thickBot="1">
       <c r="B19" s="10"/>
       <c r="C19" s="11">
         <v>10</v>
@@ -7043,7 +7440,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15">
+    <row r="20" spans="2:8">
       <c r="B20" s="6" t="s">
         <v>58</v>
       </c>
@@ -7066,7 +7463,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15">
+    <row r="21" spans="2:8">
       <c r="B21" s="13"/>
       <c r="C21" s="11">
         <v>18</v>
@@ -7087,7 +7484,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15">
+    <row r="22" spans="2:8">
       <c r="B22" s="13"/>
       <c r="C22" s="11">
         <v>16</v>
@@ -7108,7 +7505,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="15">
+    <row r="23" spans="2:8">
       <c r="B23" s="13"/>
       <c r="C23" s="11">
         <v>14</v>
@@ -7129,7 +7526,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="15.75" thickBot="1">
+    <row r="24" spans="2:8" ht="15" thickBot="1">
       <c r="B24" s="10"/>
       <c r="C24" s="11">
         <v>12</v>
@@ -7150,7 +7547,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="15">
+    <row r="25" spans="2:8">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -7173,7 +7570,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15">
+    <row r="26" spans="2:8">
       <c r="B26" s="13"/>
       <c r="C26" s="11">
         <v>18</v>
@@ -7194,7 +7591,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15">
+    <row r="27" spans="2:8">
       <c r="B27" s="13"/>
       <c r="C27" s="11">
         <v>16</v>
@@ -7215,7 +7612,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15">
+    <row r="28" spans="2:8">
       <c r="B28" s="13"/>
       <c r="C28" s="11">
         <v>14</v>
@@ -7236,7 +7633,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="15">
+    <row r="29" spans="2:8">
       <c r="B29" s="13"/>
       <c r="C29" s="11">
         <v>12</v>
@@ -7257,7 +7654,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15.75" thickBot="1">
+    <row r="30" spans="2:8" ht="15" thickBot="1">
       <c r="B30" s="10"/>
       <c r="C30" s="11">
         <v>9</v>
@@ -7278,7 +7675,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="15">
+    <row r="31" spans="2:8">
       <c r="B31" s="6" t="s">
         <v>60</v>
       </c>
@@ -7301,7 +7698,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="15">
+    <row r="32" spans="2:8">
       <c r="B32" s="13"/>
       <c r="C32" s="11">
         <v>14</v>
@@ -7322,7 +7719,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="15">
+    <row r="33" spans="2:9">
       <c r="B33" s="13"/>
       <c r="C33" s="11">
         <v>12</v>
@@ -7343,7 +7740,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="15">
+    <row r="34" spans="2:9">
       <c r="B34" s="13"/>
       <c r="C34" s="11">
         <v>10</v>
@@ -7364,7 +7761,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="15.75" thickBot="1">
+    <row r="35" spans="2:9" ht="15" thickBot="1">
       <c r="B35" s="10"/>
       <c r="C35" s="11">
         <v>9</v>
@@ -7385,7 +7782,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="15">
+    <row r="36" spans="2:9">
       <c r="B36" s="6" t="s">
         <v>61</v>
       </c>
@@ -7408,7 +7805,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="15">
+    <row r="37" spans="2:9">
       <c r="B37" s="13"/>
       <c r="C37" s="11">
         <v>11</v>
@@ -7429,7 +7826,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="15">
+    <row r="38" spans="2:9">
       <c r="B38" s="13"/>
       <c r="C38" s="11">
         <v>7</v>
@@ -7450,7 +7847,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="15.75" thickBot="1">
+    <row r="39" spans="2:9" ht="15" thickBot="1">
       <c r="B39" s="10"/>
       <c r="C39" s="11" t="s">
         <v>62</v>
@@ -7471,7 +7868,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="15">
+    <row r="40" spans="2:9">
       <c r="B40" s="6" t="s">
         <v>63</v>
       </c>
@@ -7494,7 +7891,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="28.5">
+    <row r="41" spans="2:9" ht="29">
       <c r="B41" s="13"/>
       <c r="C41" s="11">
         <v>11</v>
@@ -7515,7 +7912,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="15">
+    <row r="42" spans="2:9">
       <c r="B42" s="13"/>
       <c r="C42" s="11">
         <v>9</v>
@@ -7536,7 +7933,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="15">
+    <row r="43" spans="2:9">
       <c r="B43" s="13"/>
       <c r="C43" s="11">
         <v>7</v>
@@ -7557,7 +7954,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="29.25" thickBot="1">
+    <row r="44" spans="2:9" ht="29.5" thickBot="1">
       <c r="B44" s="10"/>
       <c r="C44" s="11" t="s">
         <v>62</v>
@@ -7578,7 +7975,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="15">
+    <row r="45" spans="2:9">
       <c r="B45" s="6" t="s">
         <v>65</v>
       </c>
@@ -7601,7 +7998,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="15.75" thickBot="1">
+    <row r="46" spans="2:9" ht="15" thickBot="1">
       <c r="B46" s="13"/>
       <c r="C46" s="11">
         <v>9</v>
@@ -7622,7 +8019,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="15.75" thickBot="1">
+    <row r="47" spans="2:9" ht="15" thickBot="1">
       <c r="B47" s="13"/>
       <c r="C47" s="11">
         <v>7</v>
@@ -7644,7 +8041,7 @@
       </c>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="2:9" ht="29.25" thickBot="1">
+    <row r="48" spans="2:9" ht="29.5" thickBot="1">
       <c r="B48" s="10"/>
       <c r="C48" s="11" t="s">
         <v>62</v>
@@ -7665,7 +8062,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="15">
+    <row r="49" spans="2:9">
       <c r="B49" s="6" t="s">
         <v>67</v>
       </c>
@@ -7688,7 +8085,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="29.25" thickBot="1">
+    <row r="50" spans="2:9" ht="29.5" thickBot="1">
       <c r="B50" s="13"/>
       <c r="C50" s="11" t="s">
         <v>68</v>
@@ -7709,7 +8106,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="15.75" thickBot="1">
+    <row r="51" spans="2:9" ht="15" thickBot="1">
       <c r="B51" s="13"/>
       <c r="C51" s="11">
         <v>9</v>
@@ -7731,7 +8128,7 @@
       </c>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="2:9" ht="28.5">
+    <row r="52" spans="2:9" ht="29">
       <c r="B52" s="13"/>
       <c r="C52" s="11" t="s">
         <v>69</v>
@@ -7752,7 +8149,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="29.25" thickBot="1">
+    <row r="53" spans="2:9" ht="29.5" thickBot="1">
       <c r="B53" s="10"/>
       <c r="C53" s="11" t="s">
         <v>62</v>
@@ -7773,7 +8170,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="28.5">
+    <row r="54" spans="2:9" ht="29">
       <c r="B54" s="6" t="s">
         <v>70</v>
       </c>
@@ -7796,7 +8193,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="28.5">
+    <row r="55" spans="2:9" ht="29">
       <c r="B55" s="13"/>
       <c r="C55" s="11" t="s">
         <v>69</v>
@@ -7817,7 +8214,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="29.25" thickBot="1">
+    <row r="56" spans="2:9" ht="29.5" thickBot="1">
       <c r="B56" s="10"/>
       <c r="C56" s="14" t="s">
         <v>62</v>
@@ -7862,7 +8259,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="15.75" thickBot="1">
+    <row r="60" spans="2:9" ht="15" thickBot="1">
       <c r="B60" s="10" t="s">
         <v>72</v>
       </c>
@@ -7885,7 +8282,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="2:9" ht="15">
+    <row r="61" spans="2:9">
       <c r="B61" s="6" t="s">
         <v>73</v>
       </c>
@@ -7908,7 +8305,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="15.75" thickBot="1">
+    <row r="62" spans="2:9" ht="15" thickBot="1">
       <c r="B62" s="10"/>
       <c r="C62" s="11">
         <v>18</v>
@@ -7929,7 +8326,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="15">
+    <row r="63" spans="2:9">
       <c r="B63" s="6" t="s">
         <v>74</v>
       </c>
@@ -7952,7 +8349,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="15.75" thickBot="1">
+    <row r="64" spans="2:9" ht="15" thickBot="1">
       <c r="B64" s="10"/>
       <c r="C64" s="11">
         <v>18</v>
@@ -7973,7 +8370,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="15">
+    <row r="65" spans="2:8">
       <c r="B65" s="6" t="s">
         <v>75</v>
       </c>
@@ -7996,7 +8393,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="15">
+    <row r="66" spans="2:8">
       <c r="B66" s="13"/>
       <c r="C66" s="11">
         <v>18</v>
@@ -8017,7 +8414,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="15">
+    <row r="67" spans="2:8">
       <c r="B67" s="13"/>
       <c r="C67" s="11">
         <v>16</v>
@@ -8038,7 +8435,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="15">
+    <row r="68" spans="2:8">
       <c r="B68" s="13"/>
       <c r="C68" s="11">
         <v>14</v>
@@ -8059,7 +8456,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="15.75" thickBot="1">
+    <row r="69" spans="2:8" ht="15" thickBot="1">
       <c r="B69" s="10"/>
       <c r="C69" s="11">
         <v>11</v>
@@ -8080,7 +8477,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="2:8" ht="15">
+    <row r="70" spans="2:8">
       <c r="B70" s="6" t="s">
         <v>76</v>
       </c>
@@ -8103,7 +8500,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="15.75" thickBot="1">
+    <row r="71" spans="2:8" ht="15" thickBot="1">
       <c r="B71" s="10"/>
       <c r="C71" s="11">
         <v>18</v>
@@ -8124,7 +8521,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="15">
+    <row r="72" spans="2:8">
       <c r="B72" s="6" t="s">
         <v>77</v>
       </c>
@@ -8147,7 +8544,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="15">
+    <row r="73" spans="2:8">
       <c r="B73" s="13"/>
       <c r="C73" s="11">
         <v>18</v>
@@ -8168,7 +8565,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="15">
+    <row r="74" spans="2:8">
       <c r="B74" s="13"/>
       <c r="C74" s="11">
         <v>14</v>
@@ -8189,7 +8586,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="15.75" thickBot="1">
+    <row r="75" spans="2:8" ht="15" thickBot="1">
       <c r="B75" s="10"/>
       <c r="C75" s="11">
         <v>11</v>
@@ -8210,7 +8607,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="15">
+    <row r="76" spans="2:8">
       <c r="B76" s="6" t="s">
         <v>78</v>
       </c>
@@ -8233,7 +8630,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="15.75" thickBot="1">
+    <row r="77" spans="2:8" ht="15" thickBot="1">
       <c r="B77" s="10"/>
       <c r="C77" s="11">
         <v>18</v>
@@ -8254,7 +8651,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="2:8" ht="15">
+    <row r="78" spans="2:8">
       <c r="B78" s="6" t="s">
         <v>79</v>
       </c>
@@ -8277,7 +8674,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="15">
+    <row r="79" spans="2:8">
       <c r="B79" s="13"/>
       <c r="C79" s="11">
         <v>18</v>
@@ -8298,7 +8695,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="15.75" thickBot="1">
+    <row r="80" spans="2:8" ht="15" thickBot="1">
       <c r="B80" s="10"/>
       <c r="C80" s="11">
         <v>14</v>
@@ -8319,7 +8716,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="2:8" ht="15.75" thickBot="1">
+    <row r="81" spans="2:8" ht="15" thickBot="1">
       <c r="B81" s="17" t="s">
         <v>81</v>
       </c>
@@ -8342,7 +8739,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="15">
+    <row r="82" spans="2:8">
       <c r="B82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8365,7 +8762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="15">
+    <row r="83" spans="2:8">
       <c r="B83" s="13"/>
       <c r="C83" s="11">
         <v>16</v>
@@ -8386,7 +8783,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="15">
+    <row r="84" spans="2:8">
       <c r="B84" s="13"/>
       <c r="C84" s="11">
         <v>14</v>
@@ -8407,7 +8804,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="15">
+    <row r="85" spans="2:8">
       <c r="B85" s="13"/>
       <c r="C85" s="11">
         <v>11</v>
@@ -8428,7 +8825,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15.75" thickBot="1">
+    <row r="86" spans="2:8" ht="15" thickBot="1">
       <c r="B86" s="10"/>
       <c r="C86" s="11">
         <v>10</v>
@@ -8446,7 +8843,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15">
+    <row r="87" spans="2:8">
       <c r="B87" s="6" t="s">
         <v>83</v>
       </c>
@@ -8469,7 +8866,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15">
+    <row r="88" spans="2:8">
       <c r="B88" s="13"/>
       <c r="C88" s="11">
         <v>18</v>
@@ -8490,7 +8887,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15">
+    <row r="89" spans="2:8">
       <c r="B89" s="13"/>
       <c r="C89" s="11">
         <v>14</v>
@@ -8511,7 +8908,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="90" spans="2:8" ht="15.75" thickBot="1">
+    <row r="90" spans="2:8" ht="15" thickBot="1">
       <c r="B90" s="10"/>
       <c r="C90" s="11">
         <v>11</v>
@@ -8532,7 +8929,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="15">
+    <row r="91" spans="2:8">
       <c r="B91" s="6" t="s">
         <v>84</v>
       </c>
@@ -8555,7 +8952,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="15">
+    <row r="92" spans="2:8">
       <c r="B92" s="13"/>
       <c r="C92" s="11">
         <v>11</v>
@@ -8576,7 +8973,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="15">
+    <row r="93" spans="2:8">
       <c r="B93" s="13"/>
       <c r="C93" s="11">
         <v>10</v>
@@ -8597,7 +8994,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="15">
+    <row r="94" spans="2:8">
       <c r="B94" s="13"/>
       <c r="C94" s="11">
         <v>7</v>
@@ -8618,7 +9015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="15.75" thickBot="1">
+    <row r="95" spans="2:8" ht="15" thickBot="1">
       <c r="B95" s="10"/>
       <c r="C95" s="11" t="s">
         <v>62</v>
@@ -8639,7 +9036,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="15.75" thickBot="1">
+    <row r="96" spans="2:8" ht="15" thickBot="1">
       <c r="B96" s="17" t="s">
         <v>85</v>
       </c>
@@ -8662,7 +9059,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="15">
+    <row r="97" spans="2:8">
       <c r="B97" s="6" t="s">
         <v>86</v>
       </c>
@@ -8685,7 +9082,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="98" spans="2:8" ht="15">
+    <row r="98" spans="2:8">
       <c r="B98" s="13"/>
       <c r="C98" s="11">
         <v>11</v>
@@ -8706,7 +9103,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="15">
+    <row r="99" spans="2:8">
       <c r="B99" s="13"/>
       <c r="C99" s="11">
         <v>9</v>
@@ -8727,7 +9124,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="15">
+    <row r="100" spans="2:8">
       <c r="B100" s="13"/>
       <c r="C100" s="11">
         <v>7</v>
@@ -8748,7 +9145,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="29.25" thickBot="1">
+    <row r="101" spans="2:8" ht="29.5" thickBot="1">
       <c r="B101" s="10"/>
       <c r="C101" s="11" t="s">
         <v>62</v>
@@ -8769,7 +9166,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="2:8" ht="15">
+    <row r="102" spans="2:8">
       <c r="B102" s="6" t="s">
         <v>87</v>
       </c>
@@ -8792,7 +9189,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="15">
+    <row r="103" spans="2:8">
       <c r="B103" s="13"/>
       <c r="C103" s="11">
         <v>11</v>
@@ -8813,7 +9210,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="28.5">
+    <row r="104" spans="2:8" ht="29">
       <c r="B104" s="13"/>
       <c r="C104" s="11">
         <v>9</v>
@@ -8834,7 +9231,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="105" spans="2:8" ht="15">
+    <row r="105" spans="2:8">
       <c r="B105" s="13"/>
       <c r="C105" s="11">
         <v>7</v>
@@ -8855,7 +9252,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="2:8" ht="29.25" thickBot="1">
+    <row r="106" spans="2:8" ht="29.5" thickBot="1">
       <c r="B106" s="10"/>
       <c r="C106" s="11" t="s">
         <v>62</v>
@@ -8876,7 +9273,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="2:8" ht="15">
+    <row r="107" spans="2:8">
       <c r="B107" s="6" t="s">
         <v>88</v>
       </c>
@@ -8899,7 +9296,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="2:8" ht="15.75" thickBot="1">
+    <row r="108" spans="2:8" ht="15" thickBot="1">
       <c r="B108" s="10"/>
       <c r="C108" s="11">
         <v>7</v>
@@ -8920,7 +9317,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="15">
+    <row r="109" spans="2:8">
       <c r="B109" s="6" t="s">
         <v>89</v>
       </c>
@@ -8943,7 +9340,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="28.5">
+    <row r="110" spans="2:8" ht="29">
       <c r="B110" s="13"/>
       <c r="C110" s="11" t="s">
         <v>68</v>
@@ -8964,7 +9361,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="111" spans="2:8" ht="28.5">
+    <row r="111" spans="2:8" ht="29">
       <c r="B111" s="13"/>
       <c r="C111" s="11" t="s">
         <v>69</v>
@@ -8985,7 +9382,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="2:8" ht="29.25" thickBot="1">
+    <row r="112" spans="2:8" ht="29.5" thickBot="1">
       <c r="B112" s="10"/>
       <c r="C112" s="11" t="s">
         <v>62</v>
@@ -9006,7 +9403,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="2:8" ht="15">
+    <row r="113" spans="2:8">
       <c r="B113" s="6" t="s">
         <v>90</v>
       </c>
@@ -9029,7 +9426,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="114" spans="2:8" ht="28.5">
+    <row r="114" spans="2:8" ht="29">
       <c r="B114" s="13"/>
       <c r="C114" s="11" t="s">
         <v>68</v>
@@ -9050,7 +9447,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="115" spans="2:8" ht="28.5">
+    <row r="115" spans="2:8" ht="29">
       <c r="B115" s="13"/>
       <c r="C115" s="11" t="s">
         <v>69</v>
@@ -9071,7 +9468,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="2:8" ht="29.25" thickBot="1">
+    <row r="116" spans="2:8" ht="29.5" thickBot="1">
       <c r="B116" s="10"/>
       <c r="C116" s="11" t="s">
         <v>62</v>
@@ -9092,7 +9489,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" spans="2:8" ht="28.5">
+    <row r="117" spans="2:8" ht="29">
       <c r="B117" s="6" t="s">
         <v>91</v>
       </c>
@@ -9115,7 +9512,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="118" spans="2:8" ht="28.5">
+    <row r="118" spans="2:8" ht="29">
       <c r="B118" s="13"/>
       <c r="C118" s="11" t="s">
         <v>69</v>
@@ -9136,7 +9533,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="2:8" ht="29.25" thickBot="1">
+    <row r="119" spans="2:8" ht="29.5" thickBot="1">
       <c r="B119" s="10"/>
       <c r="C119" s="11" t="s">
         <v>62</v>
@@ -9157,7 +9554,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="120" spans="2:8" ht="15">
+    <row r="120" spans="2:8">
       <c r="B120" s="6" t="s">
         <v>92</v>
       </c>
@@ -9180,7 +9577,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="2:8" ht="15.75" thickBot="1">
+    <row r="121" spans="2:8" ht="15" thickBot="1">
       <c r="B121" s="10"/>
       <c r="C121" s="14" t="s">
         <v>69</v>
@@ -9206,9 +9603,9 @@
     <mergeCell ref="K3:L3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1"/>
-    <hyperlink ref="N4" r:id="rId2" display="https://www.nan-steel.com/news/astm-a500-grade-b.html"/>
-    <hyperlink ref="L6" r:id="rId3" display="https://www.fortacero.com/cat_ptr/"/>
+    <hyperlink ref="L4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="N4" r:id="rId2" display="https://www.nan-steel.com/news/astm-a500-grade-b.html" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="L6" r:id="rId3" display="https://www.fortacero.com/cat_ptr/" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
@@ -9216,9 +9613,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B24:J75"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="24" spans="2:10">
       <c r="B24" t="s">
@@ -9552,9 +9949,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:W36"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="13:19">
       <c r="M2" t="s">
@@ -9786,11 +10183,13 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F38"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="B1:P68"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
+    <col min="11" max="11" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1"/>
@@ -9903,7 +10302,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="28.5">
+    <row r="14" spans="2:6" ht="29">
       <c r="B14" s="24" t="s">
         <v>234</v>
       </c>
@@ -10112,7 +10511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:14">
       <c r="B33">
         <v>2.1</v>
       </c>
@@ -10131,7 +10530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:14">
       <c r="C34">
         <f>C33+C26</f>
         <v>40</v>
@@ -10147,7 +10546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:14">
       <c r="B35">
         <v>3.1</v>
       </c>
@@ -10166,7 +10565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:14">
       <c r="C36">
         <f>C35+C27</f>
         <v>80</v>
@@ -10182,7 +10581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:14">
       <c r="B37">
         <v>4.0999999999999996</v>
       </c>
@@ -10201,7 +10600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:14">
       <c r="C38">
         <f>C37+C27</f>
         <v>120</v>
@@ -10217,16 +10616,246 @@
         <v>0</v>
       </c>
     </row>
+    <row r="43" spans="2:14">
+      <c r="K43" t="s">
+        <v>266</v>
+      </c>
+      <c r="N43" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
+      <c r="B44" t="s">
+        <v>237</v>
+      </c>
+      <c r="K44" t="s">
+        <v>267</v>
+      </c>
+      <c r="N44" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
+      <c r="B45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
+      <c r="B46" t="s">
+        <v>240</v>
+      </c>
+      <c r="K46" t="s">
+        <v>268</v>
+      </c>
+      <c r="N46" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
+      <c r="B47" t="s">
+        <v>241</v>
+      </c>
+      <c r="K47" t="s">
+        <v>269</v>
+      </c>
+      <c r="N47" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
+      <c r="B48" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" t="s">
+        <v>244</v>
+      </c>
+      <c r="K49" t="s">
+        <v>270</v>
+      </c>
+      <c r="N49" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16">
+      <c r="B50" t="s">
+        <v>245</v>
+      </c>
+      <c r="N50" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16">
+      <c r="B51" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16">
+      <c r="B53" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16">
+      <c r="B54" t="s">
+        <v>226</v>
+      </c>
+      <c r="K54" t="s">
+        <v>247</v>
+      </c>
+      <c r="O54" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16">
+      <c r="B55" t="s">
+        <v>227</v>
+      </c>
+      <c r="K55" t="s">
+        <v>248</v>
+      </c>
+      <c r="L55" t="s">
+        <v>249</v>
+      </c>
+      <c r="O55" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16">
+      <c r="B56" t="s">
+        <v>242</v>
+      </c>
+      <c r="K56" t="s">
+        <v>250</v>
+      </c>
+      <c r="L56">
+        <v>124</v>
+      </c>
+      <c r="M56">
+        <v>365</v>
+      </c>
+      <c r="N56" t="s">
+        <v>251</v>
+      </c>
+      <c r="O56">
+        <v>29</v>
+      </c>
+      <c r="P56">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16">
+      <c r="K57" t="s">
+        <v>252</v>
+      </c>
+      <c r="L57">
+        <v>69</v>
+      </c>
+      <c r="M57">
+        <v>367</v>
+      </c>
+      <c r="N57" t="s">
+        <v>228</v>
+      </c>
+      <c r="O57">
+        <v>29</v>
+      </c>
+      <c r="P57">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16">
+      <c r="K58" t="s">
+        <v>253</v>
+      </c>
+      <c r="L58">
+        <v>218</v>
+      </c>
+      <c r="M58">
+        <v>584</v>
+      </c>
+      <c r="N58" t="s">
+        <v>228</v>
+      </c>
+      <c r="O58">
+        <v>38</v>
+      </c>
+      <c r="P58">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16">
+      <c r="K59" t="s">
+        <v>254</v>
+      </c>
+      <c r="L59">
+        <v>260</v>
+      </c>
+      <c r="M59">
+        <v>728</v>
+      </c>
+      <c r="N59" t="s">
+        <v>228</v>
+      </c>
+      <c r="O59">
+        <v>54</v>
+      </c>
+      <c r="P59">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16">
+      <c r="K61" t="s">
+        <v>255</v>
+      </c>
+      <c r="O61" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16">
+      <c r="O62" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16">
+      <c r="O63" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" spans="11:12">
+      <c r="K65" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="66" spans="11:12">
+      <c r="K66" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="67" spans="11:12">
+      <c r="K67" t="s">
+        <v>263</v>
+      </c>
+      <c r="L67" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="68" spans="11:12">
+      <c r="K68" t="s">
+        <v>264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:J231"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="3" spans="2:10">
       <c r="B3" t="s">
@@ -12268,10 +12897,10 @@
     <mergeCell ref="B6:H226"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" display="https://es.aliexpress.com/item/1005006070642588.html?spm=a2g0o.detail.1000023.7.6731h1Sth1St9k&amp;gatewayAdapt=glo2esp"/>
-    <hyperlink ref="J7" r:id="rId2" display="https://es.aliexpress.com/item/1005006236153559.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.10.42b5Hp0XHp0XEL&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40000.327270.0&amp;scm_id=1007.40000.327270.0&amp;scm-url=1007.40000.327270.0&amp;pvid=8e8df423-9348-430e-bd8a-ef2b74523ad3&amp;_t=gps-id:pcDetailTopMoreOtherSeller,scm-url:1007.40000.327270.0,pvid:8e8df423-9348-430e-bd8a-ef2b74523ad3,tpp_buckets:668%232846%238115%232000&amp;pdp_npi=4%40dis%21MXN%211440.14%211440.14%21%21%21580.00%21580.00%21%402101c80217210782867234885e2967%2112000036407770943%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A&amp;search_p4p_id=202407151418067686820644873943000265_9"/>
-    <hyperlink ref="J9" r:id="rId3" display="https://es.aliexpress.com/item/1005006732452379.html?spm=a2g0o.detail.pcDetailBottomMoreOtherSeller.7.1a3d4wrx4wrxGR&amp;gps-id=pcDetailBottomMoreOtherSeller&amp;scm=1007.40000.326746.0&amp;scm_id=1007.40000.326746.0&amp;scm-url=1007.40000.326746.0&amp;pvid=b897bdac-172d-4dcc-83a0-454806878ae4&amp;_t=gps-id:pcDetailBottomMoreOtherSeller,scm-url:1007.40000.326746.0,pvid:b897bdac-172d-4dcc-83a0-454806878ae4,tpp_buckets:668%232846%238115%23870&amp;pdp_npi=4%40dis%21MXN%211253.72%21674.56%21%21%21504.92%21271.67%21%402101dee017210836143727304e969f%2112000038120783793%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailBottomMoreOtherSeller%7Cquery_from%3A"/>
-    <hyperlink ref="B231" r:id="rId4" display="https://www.amazon.com.mx/Conversi%C3%B3n-Anal%C3%B3gico-Adquisici%C3%B3n-Precisi%C3%B3n-Anal%C3%B3gicas/dp/B099KR3ZH2/ref=sr_1_4_sspa?__mk_es_MX=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=2ZSLGVRH28XV4&amp;dib=eyJ2IjoiMSJ9.4G6WaOCAu0novMMLXdnrGg.WiLun_ccVPpdns00fxZXsuGMPfwrG2LR9eMn6e7xYY4&amp;dib_tag=se&amp;keywords=adc+high+sps&amp;qid=1739164832&amp;sprefix=adc+high+sps%2Caps%2C118&amp;sr=8-4-spons&amp;ufe=app_do%3Aamzn1.fos.45030d3a-91a9-4303-890a-776dee9077c1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9tdGY&amp;psc=1"/>
+    <hyperlink ref="B4" r:id="rId1" display="https://es.aliexpress.com/item/1005006070642588.html?spm=a2g0o.detail.1000023.7.6731h1Sth1St9k&amp;gatewayAdapt=glo2esp" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="J7" r:id="rId2" display="https://es.aliexpress.com/item/1005006236153559.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.10.42b5Hp0XHp0XEL&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40000.327270.0&amp;scm_id=1007.40000.327270.0&amp;scm-url=1007.40000.327270.0&amp;pvid=8e8df423-9348-430e-bd8a-ef2b74523ad3&amp;_t=gps-id:pcDetailTopMoreOtherSeller,scm-url:1007.40000.327270.0,pvid:8e8df423-9348-430e-bd8a-ef2b74523ad3,tpp_buckets:668%232846%238115%232000&amp;pdp_npi=4%40dis%21MXN%211440.14%211440.14%21%21%21580.00%21580.00%21%402101c80217210782867234885e2967%2112000036407770943%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A&amp;search_p4p_id=202407151418067686820644873943000265_9" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="J9" r:id="rId3" display="https://es.aliexpress.com/item/1005006732452379.html?spm=a2g0o.detail.pcDetailBottomMoreOtherSeller.7.1a3d4wrx4wrxGR&amp;gps-id=pcDetailBottomMoreOtherSeller&amp;scm=1007.40000.326746.0&amp;scm_id=1007.40000.326746.0&amp;scm-url=1007.40000.326746.0&amp;pvid=b897bdac-172d-4dcc-83a0-454806878ae4&amp;_t=gps-id:pcDetailBottomMoreOtherSeller,scm-url:1007.40000.326746.0,pvid:b897bdac-172d-4dcc-83a0-454806878ae4,tpp_buckets:668%232846%238115%23870&amp;pdp_npi=4%40dis%21MXN%211253.72%21674.56%21%21%21504.92%21271.67%21%402101dee017210836143727304e969f%2112000038120783793%21rec%21MX%21%21AB&amp;utparam-url=scene%3ApcDetailBottomMoreOtherSeller%7Cquery_from%3A" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="B231" r:id="rId4" display="https://www.amazon.com.mx/Conversi%C3%B3n-Anal%C3%B3gico-Adquisici%C3%B3n-Precisi%C3%B3n-Anal%C3%B3gicas/dp/B099KR3ZH2/ref=sr_1_4_sspa?__mk_es_MX=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=2ZSLGVRH28XV4&amp;dib=eyJ2IjoiMSJ9.4G6WaOCAu0novMMLXdnrGg.WiLun_ccVPpdns00fxZXsuGMPfwrG2LR9eMn6e7xYY4&amp;dib_tag=se&amp;keywords=adc+high+sps&amp;qid=1739164832&amp;sprefix=adc+high+sps%2Caps%2C118&amp;sr=8-4-spons&amp;ufe=app_do%3Aamzn1.fos.45030d3a-91a9-4303-890a-776dee9077c1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9tdGY&amp;psc=1" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId5"/>
